--- a/SnorresMatteskjema.xlsx
+++ b/SnorresMatteskjema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43B1AFBB-8DFF-4B3E-A7B1-C4283892F6CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B0BB9A-9538-4C81-8386-084127CF1B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="501" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utregning" sheetId="2" state="hidden" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="139">
   <si>
     <t>📊 Histogram – Sentralmål i gruppert materiale</t>
   </si>
@@ -112,18 +112,9 @@
     <t>Intervall</t>
   </si>
   <si>
-    <t>AMORTISERINGSPLAN – Lånenedbetaling</t>
-  </si>
-  <si>
     <t>Lånets beløp (kr)</t>
   </si>
   <si>
-    <t>Årlig rente (%)</t>
-  </si>
-  <si>
-    <t>Låneperiode (år)</t>
-  </si>
-  <si>
     <t>År</t>
   </si>
   <si>
@@ -202,9 +193,6 @@
     <t>Grønn = beregnet svar</t>
   </si>
   <si>
-    <t>ENHETOMGJØRING - 1P/2P EKSAMEN</t>
-  </si>
-  <si>
     <t>VOLUM (Kubikkenheter)</t>
   </si>
   <si>
@@ -343,9 +331,6 @@
     <t>FREKVENSTABELL – Gjennomsnitt og Standardavvik</t>
   </si>
   <si>
-    <t>GUIDE</t>
-  </si>
-  <si>
     <t>Fyll inn Observasjon og Frekvens (blå celler). Alle beregninger skjer automatisk.</t>
   </si>
   <si>
@@ -355,54 +340,18 @@
     <t>Frekvens (f)</t>
   </si>
   <si>
-    <t>1. Fyll inn observasjoner (blå) i kolonne A</t>
-  </si>
-  <si>
     <t>Sum f·x</t>
   </si>
   <si>
-    <t>2. Fyll inn tilhørende frekvenser (blå) i kolonne B</t>
-  </si>
-  <si>
-    <t>3. Alle beregninger oppdateres automatisk</t>
-  </si>
-  <si>
     <t>Sum (x−x̄)²·f</t>
   </si>
   <si>
     <t>Varians (s²)</t>
   </si>
   <si>
-    <t>Tips:</t>
-  </si>
-  <si>
     <t>Standardavvik (s)</t>
   </si>
   <si>
-    <t>• Bruk maks 10 observasjoner</t>
-  </si>
-  <si>
-    <t>• La tomme rader stå tomme</t>
-  </si>
-  <si>
-    <t>• Formlene håndterer tomme celler</t>
-  </si>
-  <si>
-    <t>Screenshot av tabellen:</t>
-  </si>
-  <si>
-    <t>Shift + Windows + S</t>
-  </si>
-  <si>
-    <t>Screenshot med formler:</t>
-  </si>
-  <si>
-    <t>Formler → Vis formler,</t>
-  </si>
-  <si>
-    <t>ta screenshot, lim i Word</t>
-  </si>
-  <si>
     <t>Frekvenstabell</t>
   </si>
   <si>
@@ -445,9 +394,6 @@
     <t>📈 FINN NY VERDI</t>
   </si>
   <si>
-    <t xml:space="preserve">  Formel: Ny verdi = Opprinnelig verdi × (1 + Prosentvis endring / 100)</t>
-  </si>
-  <si>
     <t>Felt</t>
   </si>
   <si>
@@ -457,70 +403,37 @@
     <t>Opprinnelig verdi</t>
   </si>
   <si>
-    <t xml:space="preserve">  Skriv inn utgangsverdien din her</t>
-  </si>
-  <si>
     <t>Prosentvis endring (%)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Positiv = økning, negativ = reduksjon</t>
-  </si>
-  <si>
     <t>RESULTAT</t>
   </si>
   <si>
     <t>✅ Ny verdi</t>
   </si>
   <si>
-    <t xml:space="preserve">  Automatisk beregnet</t>
-  </si>
-  <si>
     <t>📊 Faktisk endring</t>
   </si>
   <si>
-    <t xml:space="preserve">  Differansen i absolutt verdi</t>
-  </si>
-  <si>
     <t>🔍 FINN OPPRINNELIG VERDI</t>
   </si>
   <si>
-    <t xml:space="preserve">  Formel: Opprinnelig verdi = Ny verdi ÷ (1 + Prosentvis endring / 100)</t>
-  </si>
-  <si>
     <t>Ny verdi (etter endring)</t>
   </si>
   <si>
-    <t xml:space="preserve">  Skriv inn verdien etter endringen</t>
-  </si>
-  <si>
     <t>✅ Opprinnelig verdi</t>
   </si>
   <si>
     <t>📉 FINN PROSENTVIS ENDRING</t>
   </si>
   <si>
-    <t xml:space="preserve">  Formel: % endring = (Ny verdi − Opprinnelig verdi) ÷ Opprinnelig verdi × 100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Startverdien (før endringen)</t>
-  </si>
-  <si>
     <t>Ny verdi</t>
   </si>
   <si>
-    <t xml:space="preserve">  Sluttverdien (etter endringen)</t>
-  </si>
-  <si>
     <t>✅ Prosentvis endring</t>
   </si>
   <si>
-    <t xml:space="preserve">  I prosent (%) — negativt = reduksjon</t>
-  </si>
-  <si>
     <t>🔁 Formatert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Samme som over, men med %-tegn</t>
   </si>
   <si>
     <t>Prosentregning</t>
@@ -538,6 +451,27 @@
       </rPr>
       <t>❤</t>
     </r>
+  </si>
+  <si>
+    <t>ENHETOMGJØRING</t>
+  </si>
+  <si>
+    <t>Gebyr</t>
+  </si>
+  <si>
+    <t>Gebyr (kr)</t>
+  </si>
+  <si>
+    <t>Månedlig rente (%)</t>
+  </si>
+  <si>
+    <t>Låneperiode (måned)</t>
+  </si>
+  <si>
+    <t>Terminbeløp</t>
+  </si>
+  <si>
+    <t>Lånnedbetaling</t>
   </si>
 </sst>
 </file>
@@ -764,13 +698,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="25"/>
       <color theme="0"/>
       <name val="Arial"/>
@@ -815,8 +742,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -851,12 +785,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFD5F5E3"/>
         <bgColor rgb="FFCCFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor rgb="FF333333"/>
       </patternFill>
     </fill>
     <fill>
@@ -1028,7 +956,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1094,19 +1022,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1114,20 +1029,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1151,208 +1054,201 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="14" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="14" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="14" fillId="7" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="18" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="26" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="26" fillId="19" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="14" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="14" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="33" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="16" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="8" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="28" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="32" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="15" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="15" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="14" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="14" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="16" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="21" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="14" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="16" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="16" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="29" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="26" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="33" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="15" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="15" fillId="31" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="35" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1431,14 +1327,14 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FF373A4B"/>
+      <color rgb="FF1FBB96"/>
+      <color rgb="FF2EC4A1"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFCCCCFF"/>
       <color rgb="FFFFCCCC"/>
       <color rgb="FF2E3047"/>
-      <color rgb="FF1FBB96"/>
-      <color rgb="FF373A4B"/>
       <color rgb="FFFF7C80"/>
-      <color rgb="FF2EC4A1"/>
       <color rgb="FF4E5476"/>
       <color rgb="FFCC99FF"/>
     </mruColors>
@@ -1567,9 +1463,9 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:multiLvlStrRef>
               <c:f>Histogram!$A$2:$A$21</c:f>
-            </c:strRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2967,64 +2863,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="31.8">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="31.2">
+      <c r="A2" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="31.2">
+      <c r="A3" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="31.2">
+      <c r="A4" s="44" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="31.2">
+      <c r="A5" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="31.2">
+      <c r="A6" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="45" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="31.2">
+      <c r="A7" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="49" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="18.600000000000001">
+      <c r="A11" s="48" t="s">
         <v>131</v>
-      </c>
-      <c r="B1" s="70" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="31.2">
-      <c r="A2" s="71" t="s">
-        <v>123</v>
-      </c>
-      <c r="B2" s="72" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="31.2">
-      <c r="A3" s="73" t="s">
-        <v>119</v>
-      </c>
-      <c r="B3" s="74" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="31.2">
-      <c r="A4" s="71" t="s">
-        <v>120</v>
-      </c>
-      <c r="B4" s="72" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="31.2">
-      <c r="A5" s="73" t="s">
-        <v>159</v>
-      </c>
-      <c r="B5" s="74" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="31.2">
-      <c r="A6" s="71" t="s">
-        <v>121</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="31.2">
-      <c r="A7" s="73" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="76" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18.600000000000001">
-      <c r="A11" s="75" t="s">
-        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3046,421 +2942,854 @@
   <sheetPr>
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="25.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="2" customWidth="1"/>
+    <col min="1" max="1" width="22.77734375" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.8">
-      <c r="A1" s="43" t="s">
+    <row r="1" spans="1:7" ht="25.2" customHeight="1">
+      <c r="A1" s="85" t="s">
+        <v>138</v>
+      </c>
+      <c r="B1" s="85"/>
+      <c r="C1" s="85"/>
+      <c r="D1" s="85"/>
+      <c r="E1" s="85"/>
+    </row>
+    <row r="2" spans="1:7" ht="19.2" customHeight="1">
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-    </row>
-    <row r="2" spans="1:5" ht="6" customHeight="1"/>
-    <row r="3" spans="1:5">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="10">
+        <v>2500000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4" s="11">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="21" customHeight="1">
+      <c r="A6" s="80" t="s">
+        <v>133</v>
+      </c>
+      <c r="B6" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B7" s="12">
+        <v>13385</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="6" customHeight="1"/>
+    <row r="9" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A9" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="14">
-        <v>200000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="13" t="s">
+      <c r="B9" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="15">
+      <c r="C9" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="D9" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="G9" s="42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="79">
+        <v>0</v>
+      </c>
+      <c r="B10" s="78">
+        <f>B3</f>
+        <v>2500000</v>
+      </c>
+      <c r="C10" s="15">
+        <f>$B$6</f>
+        <v>50</v>
+      </c>
+      <c r="D10" s="15">
+        <f>B10*B4%</f>
+        <v>8250</v>
+      </c>
+      <c r="E10" s="15">
+        <f>F10-C10-D10</f>
+        <v>5085</v>
+      </c>
+      <c r="F10" s="15">
+        <f>$B$7</f>
+        <v>13385</v>
+      </c>
+      <c r="G10" s="78">
+        <f>D10+E10</f>
+        <v>13335</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="79">
+        <v>1</v>
+      </c>
+      <c r="B11" s="78">
+        <f>B10-E10</f>
+        <v>2494915</v>
+      </c>
+      <c r="C11" s="15">
+        <f>$B$6</f>
+        <v>50</v>
+      </c>
+      <c r="D11" s="78">
+        <f>B11*$B$4%</f>
+        <v>8233.2194999999992</v>
+      </c>
+      <c r="E11" s="15">
+        <f t="shared" ref="E11:E33" si="0">F11-C11-D11</f>
+        <v>5101.7805000000008</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" ref="F11:F34" si="1">$B$7</f>
+        <v>13385</v>
+      </c>
+      <c r="G11" s="78">
+        <f>IFERROR(IF(OR(B11="",D11="",E11=""),0,MAX(0,B11+D11-E11)),"")</f>
+        <v>2498046.4390000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="79">
+        <v>2</v>
+      </c>
+      <c r="B12" s="78">
+        <f>B11-E11</f>
+        <v>2489813.2195000001</v>
+      </c>
+      <c r="C12" s="15">
+        <f t="shared" ref="C12:C34" si="2">$B$6</f>
+        <v>50</v>
+      </c>
+      <c r="D12" s="78">
+        <f>B12*$B$4%</f>
+        <v>8216.3836243500009</v>
+      </c>
+      <c r="E12" s="15">
+        <f t="shared" si="0"/>
+        <v>5118.6163756499991</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G12" s="78">
+        <f>IFERROR(IF(OR(B12="",D12="",E12=""),0,MAX(0,B12+D12-E12)),"")</f>
+        <v>2492910.9867487005</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="79">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="16">
+      <c r="B13" s="78">
+        <f>B12-E12</f>
+        <v>2484694.6031243503</v>
+      </c>
+      <c r="C13" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D13" s="78">
+        <f>B13*$B$4%</f>
+        <v>8199.4921903103568</v>
+      </c>
+      <c r="E13" s="15">
+        <f t="shared" si="0"/>
+        <v>5135.5078096896432</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G13" s="78">
+        <f>IFERROR(IF(OR(B13="",D13="",E13=""),0,MAX(0,B13+D13-E13)),"")</f>
+        <v>2487758.5875049708</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="79">
+        <v>4</v>
+      </c>
+      <c r="B14" s="78">
+        <f>B13-E13</f>
+        <v>2479559.0953146606</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D14" s="78">
+        <f>B14*$B$4%</f>
+        <v>8182.5450145383802</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" si="0"/>
+        <v>5152.4549854616198</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G14" s="78">
+        <f>IFERROR(IF(OR(B14="",D14="",E14=""),0,MAX(0,B14+D14-E14)),"")</f>
+        <v>2482589.1853437372</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="79">
+        <v>5</v>
+      </c>
+      <c r="B15" s="78">
+        <f>B14-E14</f>
+        <v>2474406.6403291989</v>
+      </c>
+      <c r="C15" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D15" s="78">
+        <f>B15*$B$4%</f>
+        <v>8165.5419130863565</v>
+      </c>
+      <c r="E15" s="15">
+        <f t="shared" si="0"/>
+        <v>5169.4580869136435</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G15" s="78">
+        <f>IFERROR(IF(OR(B15="",D15="",E15=""),0,MAX(0,B15+D15-E15)),"")</f>
+        <v>2477402.724155372</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="79">
+        <v>6</v>
+      </c>
+      <c r="B16" s="78">
+        <f>B15-E15</f>
+        <v>2469237.1822422855</v>
+      </c>
+      <c r="C16" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D16" s="78">
+        <f>B16*$B$4%</f>
+        <v>8148.4827013995418</v>
+      </c>
+      <c r="E16" s="15">
+        <f t="shared" si="0"/>
+        <v>5186.5172986004582</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G16" s="78">
+        <f>IFERROR(IF(OR(B16="",D16="",E16=""),0,MAX(0,B16+D16-E16)),"")</f>
+        <v>2472199.1476450842</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="79">
+        <v>7</v>
+      </c>
+      <c r="B17" s="78">
+        <f>B16-E16</f>
+        <v>2464050.6649436848</v>
+      </c>
+      <c r="C17" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D17" s="78">
+        <f>B17*$B$4%</f>
+        <v>8131.3671943141599</v>
+      </c>
+      <c r="E17" s="15">
+        <f t="shared" si="0"/>
+        <v>5203.6328056858401</v>
+      </c>
+      <c r="F17" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G17" s="78">
+        <f>IFERROR(IF(OR(B17="",D17="",E17=""),0,MAX(0,B17+D17-E17)),"")</f>
+        <v>2466978.3993323129</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="79">
+        <v>8</v>
+      </c>
+      <c r="B18" s="78">
+        <f>B17-E17</f>
+        <v>2458847.0321379988</v>
+      </c>
+      <c r="C18" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D18" s="78">
+        <f>B18*$B$4%</f>
+        <v>8114.1952060553958</v>
+      </c>
+      <c r="E18" s="15">
+        <f t="shared" si="0"/>
+        <v>5220.8047939446042</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G18" s="78">
+        <f>IFERROR(IF(OR(B18="",D18="",E18=""),0,MAX(0,B18+D18-E18)),"")</f>
+        <v>2461740.4225501097</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="79">
+        <v>9</v>
+      </c>
+      <c r="B19" s="78">
+        <f>B18-E18</f>
+        <v>2453626.2273440543</v>
+      </c>
+      <c r="C19" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D19" s="78">
+        <f>B19*$B$4%</f>
+        <v>8096.9665502353791</v>
+      </c>
+      <c r="E19" s="15">
+        <f t="shared" si="0"/>
+        <v>5238.0334497646209</v>
+      </c>
+      <c r="F19" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G19" s="78">
+        <f>IFERROR(IF(OR(B19="",D19="",E19=""),0,MAX(0,B19+D19-E19)),"")</f>
+        <v>2456485.1604445246</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="79">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="6" customHeight="1"/>
-    <row r="7" spans="1:5">
-      <c r="A7" s="17"/>
-      <c r="B7" s="36"/>
-    </row>
-    <row r="8" spans="1:5" ht="6" customHeight="1"/>
-    <row r="9" spans="1:5" ht="21.75" customHeight="1">
-      <c r="A9" s="67" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="67" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="67" t="s">
+      <c r="B20" s="78">
+        <f>B19-E19</f>
+        <v>2448388.1938942894</v>
+      </c>
+      <c r="C20" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D20" s="78">
+        <f>B20*$B$4%</f>
+        <v>8079.6810398511552</v>
+      </c>
+      <c r="E20" s="15">
+        <f t="shared" si="0"/>
+        <v>5255.3189601488448</v>
+      </c>
+      <c r="F20" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G20" s="78">
+        <f>IFERROR(IF(OR(B20="",D20="",E20=""),0,MAX(0,B20+D20-E20)),"")</f>
+        <v>2451212.5559739918</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="79">
+        <v>11</v>
+      </c>
+      <c r="B21" s="78">
+        <f>B20-E20</f>
+        <v>2443132.8749341406</v>
+      </c>
+      <c r="C21" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D21" s="78">
+        <f>B21*$B$4%</f>
+        <v>8062.3384872826637</v>
+      </c>
+      <c r="E21" s="15">
+        <f t="shared" si="0"/>
+        <v>5272.6615127173363</v>
+      </c>
+      <c r="F21" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G21" s="78">
+        <f>IFERROR(IF(OR(B21="",D21="",E21=""),0,MAX(0,B21+D21-E21)),"")</f>
+        <v>2445922.5519087063</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="79">
+        <v>12</v>
+      </c>
+      <c r="B22" s="78">
+        <f>B21-E21</f>
+        <v>2437860.2134214235</v>
+      </c>
+      <c r="C22" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D22" s="78">
+        <f>B22*$B$4%</f>
+        <v>8044.9387042906974</v>
+      </c>
+      <c r="E22" s="15">
+        <f t="shared" si="0"/>
+        <v>5290.0612957093026</v>
+      </c>
+      <c r="F22" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G22" s="78">
+        <f>IFERROR(IF(OR(B22="",D22="",E22=""),0,MAX(0,B22+D22-E22)),"")</f>
+        <v>2440615.0908300052</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="79">
+        <v>13</v>
+      </c>
+      <c r="B23" s="78">
+        <f>B22-E22</f>
+        <v>2432570.1521257143</v>
+      </c>
+      <c r="C23" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D23" s="78">
+        <f>B23*$B$4%</f>
+        <v>8027.4815020148571</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="0"/>
+        <v>5307.5184979851429</v>
+      </c>
+      <c r="F23" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G23" s="78">
+        <f>IFERROR(IF(OR(B23="",D23="",E23=""),0,MAX(0,B23+D23-E23)),"")</f>
+        <v>2435290.1151297437</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="79">
+        <v>14</v>
+      </c>
+      <c r="B24" s="15">
+        <f>B23-E23</f>
+        <v>2427262.633627729</v>
+      </c>
+      <c r="C24" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D24" s="78">
+        <f>B24*$B$4%</f>
+        <v>8009.9666909715061</v>
+      </c>
+      <c r="E24" s="15">
+        <f t="shared" si="0"/>
+        <v>5325.0333090284939</v>
+      </c>
+      <c r="F24" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G24" s="15">
+        <f>IFERROR(IF(OR(B24="",D24="",E24=""),0,MAX(0,B24+D24-E24)),"")</f>
+        <v>2429947.5670096721</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="79">
+        <v>15</v>
+      </c>
+      <c r="B25" s="15">
+        <f>B24-E24</f>
+        <v>2421937.6003187005</v>
+      </c>
+      <c r="C25" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D25" s="78">
+        <f>B25*$B$4%</f>
+        <v>7992.3940810517115</v>
+      </c>
+      <c r="E25" s="15">
+        <f t="shared" si="0"/>
+        <v>5342.6059189482885</v>
+      </c>
+      <c r="F25" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G25" s="15">
+        <f>IFERROR(IF(OR(B25="",D25="",E25=""),0,MAX(0,B25+D25-E25)),"")</f>
+        <v>2424587.3884808044</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A26" s="79">
+        <v>16</v>
+      </c>
+      <c r="B26" s="15">
+        <f>B25-E25</f>
+        <v>2416594.9943997525</v>
+      </c>
+      <c r="C26" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D26" s="78">
+        <f>B26*$B$4%</f>
+        <v>7974.7634815191832</v>
+      </c>
+      <c r="E26" s="15">
+        <f t="shared" si="0"/>
+        <v>5360.2365184808168</v>
+      </c>
+      <c r="F26" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G26" s="15">
+        <f>IFERROR(IF(OR(B26="",D26="",E26=""),0,MAX(0,B26+D26-E26)),"")</f>
+        <v>2419209.5213627908</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="79">
+        <v>17</v>
+      </c>
+      <c r="B27" s="15">
+        <f>B26-E26</f>
+        <v>2411234.7578812717</v>
+      </c>
+      <c r="C27" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D27" s="78">
+        <f>B27*$B$4%</f>
+        <v>7957.0747010081968</v>
+      </c>
+      <c r="E27" s="15">
+        <f t="shared" si="0"/>
+        <v>5377.9252989918032</v>
+      </c>
+      <c r="F27" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G27" s="15">
+        <f>IFERROR(IF(OR(B27="",D27="",E27=""),0,MAX(0,B27+D27-E27)),"")</f>
+        <v>2413813.9072832884</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="79">
+        <v>18</v>
+      </c>
+      <c r="B28" s="15">
+        <f>B27-E27</f>
+        <v>2405856.83258228</v>
+      </c>
+      <c r="C28" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D28" s="78">
+        <f>B28*$B$4%</f>
+        <v>7939.3275475215241</v>
+      </c>
+      <c r="E28" s="15">
+        <f t="shared" si="0"/>
+        <v>5395.6724524784759</v>
+      </c>
+      <c r="F28" s="15">
+        <f>$B$7</f>
+        <v>13385</v>
+      </c>
+      <c r="G28" s="15">
+        <f>IFERROR(IF(OR(B28="",D28="",E28=""),0,MAX(0,B28+D28-E28)),"")</f>
+        <v>2408400.4876773227</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="79">
+        <v>19</v>
+      </c>
+      <c r="B29" s="15">
+        <f>B28-E28</f>
+        <v>2400461.1601298014</v>
+      </c>
+      <c r="C29" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D29" s="78">
+        <f>B29*$B$4%</f>
+        <v>7921.5218284283446</v>
+      </c>
+      <c r="E29" s="15">
+        <f t="shared" si="0"/>
+        <v>5413.4781715716554</v>
+      </c>
+      <c r="F29" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G29" s="15">
+        <f>IFERROR(IF(OR(B29="",D29="",E29=""),0,MAX(0,B29+D29-E29)),"")</f>
+        <v>2402969.2037866581</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="79">
+        <v>20</v>
+      </c>
+      <c r="B30" s="15">
+        <f>B29-E29</f>
+        <v>2395047.6819582297</v>
+      </c>
+      <c r="C30" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D30" s="78">
+        <f>B30*$B$4%</f>
+        <v>7903.6573504621583</v>
+      </c>
+      <c r="E30" s="15">
+        <f t="shared" si="0"/>
+        <v>5431.3426495378417</v>
+      </c>
+      <c r="F30" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G30" s="15">
+        <f>IFERROR(IF(OR(B30="",D30="",E30=""),0,MAX(0,B30+D30-E30)),"")</f>
+        <v>2397519.9966591536</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="79">
+        <v>21</v>
+      </c>
+      <c r="B31" s="15">
+        <f>B30-E30</f>
+        <v>2389616.3393086917</v>
+      </c>
+      <c r="C31" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D31" s="78">
+        <f>B31*$B$4%</f>
+        <v>7885.733919718682</v>
+      </c>
+      <c r="E31" s="15">
+        <f>F31-C31-D31</f>
+        <v>5449.266080281318</v>
+      </c>
+      <c r="F31" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G31" s="15">
+        <f>IFERROR(IF(OR(B31="",D31="",E31=""),0,MAX(0,B31+D31-E31)),"")</f>
+        <v>2392052.8071481292</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="79">
+        <v>22</v>
+      </c>
+      <c r="B32" s="15">
+        <f>B31-E31</f>
+        <v>2384167.0732284104</v>
+      </c>
+      <c r="C32" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D32" s="78">
+        <f>B32*$B$4%</f>
+        <v>7867.751341653754</v>
+      </c>
+      <c r="E32" s="15">
+        <f t="shared" si="0"/>
+        <v>5467.248658346246</v>
+      </c>
+      <c r="F32" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G32" s="15">
+        <f>IFERROR(IF(OR(B32="",D32="",E32=""),0,MAX(0,B32+D32-E32)),"")</f>
+        <v>2386567.5759117175</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="79">
+        <v>23</v>
+      </c>
+      <c r="B33" s="15">
+        <f>B32-E32</f>
+        <v>2378699.824570064</v>
+      </c>
+      <c r="C33" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D33" s="78">
+        <f>B33*$B$4%</f>
+        <v>7849.7094210812111</v>
+      </c>
+      <c r="E33" s="15">
+        <f t="shared" si="0"/>
+        <v>5485.2905789187889</v>
+      </c>
+      <c r="F33" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G33" s="15">
+        <f>IFERROR(IF(OR(B33="",D33="",E33=""),0,MAX(0,B33+D33-E33)),"")</f>
+        <v>2381064.243412226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="79">
+        <v>24</v>
+      </c>
+      <c r="B34" s="15">
+        <f>B33-E33</f>
+        <v>2373214.533991145</v>
+      </c>
+      <c r="C34" s="15">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="D34" s="78">
+        <f>B34*$B$4%</f>
+        <v>7831.6079621707786</v>
+      </c>
+      <c r="E34" s="15">
+        <f t="shared" ref="E34" si="3">F34-C34-D34</f>
+        <v>5503.3920378292214</v>
+      </c>
+      <c r="F34" s="15">
+        <f t="shared" si="1"/>
+        <v>13385</v>
+      </c>
+      <c r="G34" s="15">
+        <f>IFERROR(IF(OR(B34="",D34="",E34=""),0,MAX(0,B34+D34-E34)),"")</f>
+        <v>2375542.7499154862</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="67" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="67" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="19">
-        <v>1</v>
-      </c>
-      <c r="B10" s="20">
-        <f>B3</f>
-        <v>200000</v>
-      </c>
-      <c r="C10" s="20">
-        <f>B10*B4%</f>
-        <v>6000</v>
-      </c>
-      <c r="D10" s="20">
-        <f>B3/B5</f>
-        <v>20000</v>
-      </c>
-      <c r="E10" s="20">
-        <f>C10+D10</f>
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="21">
-        <v>2</v>
-      </c>
-      <c r="B11" s="22">
-        <f>B10-D10</f>
-        <v>180000</v>
-      </c>
-      <c r="C11" s="22">
-        <f>B11*$B$4%</f>
-        <v>5400</v>
-      </c>
-      <c r="D11" s="22">
-        <f>$B$3/$B$5</f>
-        <v>20000</v>
-      </c>
-      <c r="E11" s="22">
-        <f t="shared" ref="E11:E25" si="0">IFERROR(IF(OR(B11="",C11="",D11=""),0,MAX(0,B11+C11-D11)),"")</f>
-        <v>165400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="19">
-        <v>3</v>
-      </c>
-      <c r="B12" s="20">
-        <f>B11-D11</f>
-        <v>160000</v>
-      </c>
-      <c r="C12" s="22">
-        <f>B12*$B$4%</f>
-        <v>4800</v>
-      </c>
-      <c r="D12" s="22">
-        <f t="shared" ref="D12:D24" si="1">$B$3/$B$5</f>
-        <v>20000</v>
-      </c>
-      <c r="E12" s="20">
-        <f t="shared" si="0"/>
-        <v>144800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="21">
-        <v>4</v>
-      </c>
-      <c r="B13" s="22">
-        <f>B12-D12</f>
-        <v>140000</v>
-      </c>
-      <c r="C13" s="22">
-        <f>B13*$B$4%</f>
-        <v>4200</v>
-      </c>
-      <c r="D13" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E13" s="22">
-        <f t="shared" si="0"/>
-        <v>124200</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="19">
-        <v>5</v>
-      </c>
-      <c r="B14" s="20">
-        <f>B13-D13</f>
-        <v>120000</v>
-      </c>
-      <c r="C14" s="22">
-        <f t="shared" ref="C14:C24" si="2">B14*$B$4%</f>
-        <v>3600</v>
-      </c>
-      <c r="D14" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E14" s="20">
-        <f t="shared" si="0"/>
-        <v>103600</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="21">
-        <v>6</v>
-      </c>
-      <c r="B15" s="22">
-        <f t="shared" ref="B15:B26" si="3">B14-D14</f>
-        <v>100000</v>
-      </c>
-      <c r="C15" s="22">
-        <f t="shared" si="2"/>
-        <v>3000</v>
-      </c>
-      <c r="D15" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E15" s="22">
-        <f t="shared" si="0"/>
-        <v>83000</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="19">
-        <v>7</v>
-      </c>
-      <c r="B16" s="20">
-        <f t="shared" si="3"/>
-        <v>80000</v>
-      </c>
-      <c r="C16" s="22">
-        <f t="shared" si="2"/>
-        <v>2400</v>
-      </c>
-      <c r="D16" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E16" s="20">
-        <f t="shared" si="0"/>
-        <v>62400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="21">
-        <v>8</v>
-      </c>
-      <c r="B17" s="22">
-        <f t="shared" si="3"/>
-        <v>60000</v>
-      </c>
-      <c r="C17" s="22">
-        <f t="shared" si="2"/>
-        <v>1800</v>
-      </c>
-      <c r="D17" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E17" s="22">
-        <f t="shared" si="0"/>
-        <v>41800</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="19">
-        <v>9</v>
-      </c>
-      <c r="B18" s="20">
-        <f t="shared" si="3"/>
-        <v>40000</v>
-      </c>
-      <c r="C18" s="22">
-        <f t="shared" si="2"/>
-        <v>1200</v>
-      </c>
-      <c r="D18" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E18" s="20">
-        <f t="shared" si="0"/>
-        <v>21200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="21">
-        <v>10</v>
-      </c>
-      <c r="B19" s="22">
-        <f t="shared" si="3"/>
-        <v>20000</v>
-      </c>
-      <c r="C19" s="22">
-        <f t="shared" si="2"/>
-        <v>600</v>
-      </c>
-      <c r="D19" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E19" s="22">
-        <f t="shared" si="0"/>
-        <v>600</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="19">
-        <v>11</v>
-      </c>
-      <c r="B20" s="20">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="C20" s="22">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="D20" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E20" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="21">
-        <v>12</v>
-      </c>
-      <c r="B21" s="22">
-        <f t="shared" si="3"/>
-        <v>-20000</v>
-      </c>
-      <c r="C21" s="22">
-        <f t="shared" si="2"/>
-        <v>-600</v>
-      </c>
-      <c r="D21" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E21" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="19">
-        <v>13</v>
-      </c>
-      <c r="B22" s="20">
-        <f t="shared" si="3"/>
-        <v>-40000</v>
-      </c>
-      <c r="C22" s="22">
-        <f t="shared" si="2"/>
-        <v>-1200</v>
-      </c>
-      <c r="D22" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E22" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="21">
-        <v>14</v>
-      </c>
-      <c r="B23" s="22">
-        <f t="shared" si="3"/>
-        <v>-60000</v>
-      </c>
-      <c r="C23" s="22">
-        <f t="shared" si="2"/>
-        <v>-1800</v>
-      </c>
-      <c r="D23" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E23" s="22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="19">
-        <v>15</v>
-      </c>
-      <c r="B24" s="20">
-        <f t="shared" si="3"/>
-        <v>-80000</v>
-      </c>
-      <c r="C24" s="22">
-        <f t="shared" si="2"/>
-        <v>-2400</v>
-      </c>
-      <c r="D24" s="22">
-        <f t="shared" si="1"/>
-        <v>20000</v>
-      </c>
-      <c r="E24" s="20">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A26" s="77" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="78">
-        <f>SUM(B10:B24)</f>
-        <v>900000</v>
-      </c>
-      <c r="C26" s="78">
-        <f>SUM(C10:C24)</f>
-        <v>27000</v>
-      </c>
-      <c r="D26" s="78">
-        <f>SUM(D10:D24)</f>
-        <v>300000</v>
-      </c>
-      <c r="E26" s="78">
-        <f>IFERROR(E24,"")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" ht="24" customHeight="1">
-      <c r="A28" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
-      <c r="D28" s="23"/>
-      <c r="E28" s="23"/>
+      <c r="B38" s="51">
+        <f>SUM(B23:B36)</f>
+        <v>28836663.584121786</v>
+      </c>
+      <c r="C38" s="51"/>
+      <c r="D38" s="51">
+        <f>SUM(D23:D36)</f>
+        <v>95160.989827601908</v>
+      </c>
+      <c r="E38" s="51">
+        <f>SUM(E23:E36)</f>
+        <v>64859.010172398099</v>
+      </c>
+      <c r="F38" s="51">
+        <f>IFERROR(F36,"")</f>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3472,7 +3801,7 @@
   <sheetPr>
     <tabColor rgb="FFCCCCFF"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.5546875" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -3486,303 +3815,248 @@
     <col min="9" max="9" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.399999999999999">
-      <c r="A1" s="68" t="s">
+    <row r="1" spans="1:8" ht="17.399999999999999">
+      <c r="A1" s="60" t="s">
+        <v>94</v>
+      </c>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="61" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="25"/>
+      <c r="F3" s="25"/>
+      <c r="G3" s="25"/>
+      <c r="H3" s="25"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="25"/>
+      <c r="F4" s="62" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="62"/>
+      <c r="H4" s="25"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="26"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="28" t="str">
+        <f t="shared" ref="C5:C14" si="0">IFERROR(IF(B5="","",A5*B5),"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="29" t="str">
+        <f t="shared" ref="D5:D14" si="1">IFERROR(IF(OR(A5="",B5=""),"",(A5-$G$7)^2*B5),"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="25"/>
+      <c r="F5" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="31">
+        <f>B15</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="25"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="32"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="D6" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E6" s="25"/>
+      <c r="F6" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="46" t="s">
+      <c r="G6" s="28">
+        <f>C15</f>
+        <v>0</v>
+      </c>
+      <c r="H6" s="25"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="26"/>
+      <c r="B7" s="27"/>
+      <c r="C7" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="D7" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="E7" s="25"/>
+      <c r="F7" s="30" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="37" t="str">
+        <f>IFERROR(C15/B15,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="25"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="32"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="D8" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F8" s="36" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="47" t="s">
+      <c r="G8" s="29">
+        <f>IFERROR(D15,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="26"/>
+      <c r="B9" s="27"/>
+      <c r="C9" s="28" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="D9" s="29" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F9" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="46"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="45"/>
-      <c r="B3" s="45"/>
-      <c r="C3" s="45"/>
-      <c r="D3" s="45"/>
-      <c r="E3" s="45"/>
-      <c r="F3" s="45"/>
-      <c r="G3" s="45"/>
-      <c r="H3" s="45"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="18" t="s">
+      <c r="G9" s="38">
+        <f>IFERROR(D15/(B15-1),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="32"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="34" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="D10" s="35" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="F10" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>130</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>129</v>
-      </c>
-      <c r="E4" s="45"/>
-      <c r="F4" s="48" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="48"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="49" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="26.4">
-      <c r="A5" s="50"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="52" t="str">
-        <f t="shared" ref="C5:C14" si="0">IFERROR(IF(B5="","",A5*B5),"")</f>
-        <v/>
-      </c>
-      <c r="D5" s="53" t="str">
-        <f t="shared" ref="D5:D14" si="1">IFERROR(IF(OR(A5="",B5=""),"",(A5-$G$7)^2*B5),"")</f>
-        <v/>
-      </c>
-      <c r="E5" s="45"/>
-      <c r="F5" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="55">
-        <f>B15</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="45"/>
-      <c r="I5" s="56" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="26.4">
-      <c r="A6" s="57"/>
-      <c r="B6" s="58"/>
-      <c r="C6" s="59" t="str">
+      <c r="G10" s="28">
+        <f>IFERROR(SQRT(D15/(B15-1)),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="26"/>
+      <c r="B11" s="27"/>
+      <c r="C11" s="28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D6" s="60" t="str">
+      <c r="D11" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E6" s="45"/>
-      <c r="F6" s="61" t="s">
-        <v>104</v>
-      </c>
-      <c r="G6" s="52">
-        <f>C15</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="45"/>
-      <c r="I6" s="56" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="26.4">
-      <c r="A7" s="50"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="52" t="str">
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="32"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D7" s="53" t="str">
+      <c r="D12" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E7" s="45"/>
-      <c r="F7" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="G7" s="62" t="str">
-        <f>IFERROR(C15/B15,"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="45"/>
-      <c r="I7" s="56" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="57"/>
-      <c r="B8" s="58"/>
-      <c r="C8" s="59" t="str">
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="28" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D8" s="60" t="str">
+      <c r="D13" s="29" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F8" s="61" t="s">
-        <v>107</v>
-      </c>
-      <c r="G8" s="53">
-        <f>IFERROR(D15,"")</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="56"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="50"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52" t="str">
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="32"/>
+      <c r="B14" s="33"/>
+      <c r="C14" s="34" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="D9" s="53" t="str">
+      <c r="D14" s="35" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="F9" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="G9" s="63">
-        <f>IFERROR(D15/(B15-1),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="49" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="57"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="59" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D10" s="60" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="61" t="s">
-        <v>110</v>
-      </c>
-      <c r="G10" s="52">
-        <f>IFERROR(SQRT(D15/(B15-1)),"")</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="56" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="50"/>
-      <c r="B11" s="51"/>
-      <c r="C11" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D11" s="53" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I11" s="56" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="57"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="59" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D12" s="60" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I12" s="56" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="50"/>
-      <c r="B13" s="51"/>
-      <c r="C13" s="52" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D13" s="53" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I13" s="56"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="57"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="59" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="D14" s="60" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="B15" s="64">
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="39">
         <f>SUM(B5:B14)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="65">
+      <c r="C15" s="40">
         <f>SUM(C5:C14)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="66">
+      <c r="D15" s="41">
         <f>IFERROR(SUM(D5:D14),"")</f>
         <v>0</v>
       </c>
-      <c r="I15" s="56" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="I16" s="56"/>
-    </row>
-    <row r="17" spans="9:9">
-      <c r="I17" s="49" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" spans="9:9">
-      <c r="I18" s="56" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="19" spans="9:9">
-      <c r="I19" s="56" t="s">
-        <v>118</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="I1:I2"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="F4:G4"/>
   </mergeCells>
@@ -3809,220 +4083,220 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="22.8">
-      <c r="B2" s="69" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="B2" s="70" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
     </row>
     <row r="3" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="4" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B4" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
-      <c r="F4" s="24"/>
+      <c r="B4" s="71" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="71"/>
+      <c r="D4" s="71"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="71"/>
     </row>
     <row r="5" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="6" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B6" s="25" t="s">
+      <c r="B6" s="67" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="67"/>
+      <c r="D6" s="67"/>
+      <c r="E6" s="67"/>
+      <c r="F6" s="67"/>
+    </row>
+    <row r="7" spans="2:6" ht="21.75" customHeight="1">
+      <c r="B7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="15.6">
+      <c r="B8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
-    </row>
-    <row r="7" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B7" s="26" t="s">
+      <c r="C8" s="19">
+        <v>3</v>
+      </c>
+      <c r="E8" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="F8" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="16.8">
+      <c r="B9" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="27"/>
-      <c r="E7" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="2:6" ht="15.6">
-      <c r="B8" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="29">
-        <v>3</v>
-      </c>
-      <c r="E8" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="2:6" ht="16.8">
-      <c r="B9" s="30" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="30"/>
-      <c r="E9" s="31">
+      <c r="C9" s="68"/>
+      <c r="E9" s="69">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(F8),C8&gt;0,F8&gt;0),SQRT(C8^2+F8^2),"Fyll inn a og b")</f>
         <v>5</v>
       </c>
-      <c r="F9" s="31"/>
+      <c r="F9" s="69"/>
     </row>
     <row r="10" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B10" s="32" t="s">
-        <v>41</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
+      <c r="B10" s="63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="12" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B12" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
+      <c r="B12" s="67" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
     </row>
     <row r="13" spans="2:6" ht="9.75" customHeight="1">
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="17"/>
+      <c r="E13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="15.6">
+      <c r="B14" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="19">
+        <v>5</v>
+      </c>
+      <c r="E14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="27"/>
-      <c r="E13" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="26" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6" ht="15.6">
-      <c r="B14" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="29">
-        <v>5</v>
-      </c>
-      <c r="E14" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="F14" s="29">
+      <c r="F14" s="19">
         <v>4</v>
       </c>
     </row>
     <row r="15" spans="2:6" ht="16.8">
-      <c r="B15" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="C15" s="30"/>
-      <c r="E15" s="31">
+      <c r="B15" s="68" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="68"/>
+      <c r="E15" s="69">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(F14),C14&gt;0,F14&gt;0,C14&gt;F14),SQRT(C14^2-F14^2),IF(C14&lt;=F14,"c må være større enn b","Fyll inn c og b"))</f>
         <v>3</v>
       </c>
-      <c r="F15" s="31"/>
+      <c r="F15" s="69"/>
     </row>
     <row r="16" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B16" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="32"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
+      <c r="B16" s="63" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="63"/>
+      <c r="D16" s="63"/>
+      <c r="E16" s="63"/>
+      <c r="F16" s="63"/>
     </row>
     <row r="17" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="18" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B18" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
+      <c r="B18" s="67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
     </row>
     <row r="19" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B19" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="27"/>
-      <c r="E19" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>37</v>
+      <c r="B19" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="17"/>
+      <c r="E19" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="2:6" ht="15.6">
-      <c r="B20" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="29">
+      <c r="B20" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="19">
         <v>5</v>
       </c>
-      <c r="E20" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="F20" s="29">
+      <c r="E20" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="19">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="2:6" ht="16.8">
-      <c r="B21" s="30" t="s">
-        <v>47</v>
-      </c>
-      <c r="C21" s="30"/>
-      <c r="E21" s="31">
+      <c r="B21" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" s="68"/>
+      <c r="E21" s="69">
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(F20),C20&gt;0,F20&gt;0,C20&gt;F20),SQRT(C20^2-F20^2),IF(C20&lt;=F20,"c må være større enn a","Fyll inn c og a"))</f>
         <v>4</v>
       </c>
-      <c r="F21" s="31"/>
+      <c r="F21" s="69"/>
     </row>
     <row r="22" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B22" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="C22" s="32"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="32"/>
+      <c r="B22" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
+      <c r="F22" s="63"/>
     </row>
     <row r="23" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="24" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B24" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="33"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
+      <c r="B24" s="64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="64"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="64"/>
     </row>
     <row r="25" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B25" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="34"/>
-      <c r="E25" s="35" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="35"/>
+      <c r="B25" s="65" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="65"/>
+      <c r="E25" s="66" t="s">
+        <v>48</v>
+      </c>
+      <c r="F25" s="66"/>
     </row>
     <row r="26" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="27" spans="2:6" ht="21.75" customHeight="1"/>
@@ -4040,6 +4314,12 @@
     <row r="39" ht="21.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:C25"/>
@@ -4051,12 +4331,6 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="B10:F10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4068,271 +4342,197 @@
   <sheetPr>
     <tabColor rgb="FFFFCCCC"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="21.6640625" customWidth="1"/>
+    <col min="1" max="1" width="41.6640625" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.8">
-      <c r="A1" s="79" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="80" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="B3" s="90" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="90" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="83" t="s">
-        <v>136</v>
-      </c>
-      <c r="B4" s="84">
+    <row r="1" spans="1:2" ht="16.8">
+      <c r="A1" s="83" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="83"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B4" s="55">
         <v>1000</v>
       </c>
-      <c r="C4" s="85" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="83" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="84">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="B5" s="55">
         <v>25</v>
       </c>
-      <c r="C5" s="85" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="83" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="88">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="82"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="57">
         <f>B4*(1+B5/100)</f>
         <v>1250</v>
       </c>
-      <c r="C7" s="85" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="83" t="s">
-        <v>143</v>
-      </c>
-      <c r="B8" s="88">
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="B8" s="57">
         <f>B7-B4</f>
         <v>250</v>
       </c>
-      <c r="C8" s="85" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="16.8">
-      <c r="A11" s="79" t="s">
-        <v>145</v>
-      </c>
-      <c r="B11" s="79"/>
-      <c r="C11" s="79"/>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="80" t="s">
-        <v>146</v>
-      </c>
-      <c r="B12" s="80"/>
-      <c r="C12" s="80"/>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="B13" s="90" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="90" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="83" t="s">
-        <v>147</v>
-      </c>
-      <c r="B14" s="84">
+    </row>
+    <row r="11" spans="1:2" ht="16.8" customHeight="1">
+      <c r="A11" s="83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B11" s="83"/>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="84"/>
+      <c r="B12" s="84"/>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="B13" s="59" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="54" t="s">
+        <v>124</v>
+      </c>
+      <c r="B14" s="55">
         <v>1250</v>
       </c>
-      <c r="C14" s="85" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="83" t="s">
-        <v>138</v>
-      </c>
-      <c r="B15" s="84">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="54" t="s">
+        <v>119</v>
+      </c>
+      <c r="B15" s="55">
         <v>25</v>
       </c>
-      <c r="C15" s="85" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="B16" s="86"/>
-      <c r="C16" s="86"/>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="83" t="s">
-        <v>149</v>
-      </c>
-      <c r="B17" s="88">
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="82"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="54" t="s">
+        <v>125</v>
+      </c>
+      <c r="B17" s="57">
         <f>IF(1+B15/100=0,"Ugyldig: 0%",B14/(1+B15/100))</f>
         <v>1000</v>
       </c>
-      <c r="C17" s="85" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="83" t="s">
-        <v>143</v>
-      </c>
-      <c r="B18" s="88">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="B18" s="57">
         <f>IF(ISNUMBER(B17),B14-B17,"")</f>
         <v>250</v>
       </c>
-      <c r="C18" s="85" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="16.8">
-      <c r="A21" s="79" t="s">
-        <v>150</v>
-      </c>
-      <c r="B21" s="79"/>
-      <c r="C21" s="79"/>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="80" t="s">
-        <v>151</v>
-      </c>
-      <c r="B22" s="80"/>
-      <c r="C22" s="80"/>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="81" t="s">
-        <v>134</v>
-      </c>
-      <c r="B23" s="82" t="s">
-        <v>135</v>
-      </c>
-      <c r="C23" s="82" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="83" t="s">
-        <v>136</v>
-      </c>
-      <c r="B24" s="84">
+    </row>
+    <row r="21" spans="1:2" ht="16.8" customHeight="1">
+      <c r="A21" s="83" t="s">
+        <v>126</v>
+      </c>
+      <c r="B21" s="83"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="84"/>
+      <c r="B22" s="84"/>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="52" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="53" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="54" t="s">
+        <v>118</v>
+      </c>
+      <c r="B24" s="55">
         <v>1000</v>
       </c>
-      <c r="C24" s="85" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="83" t="s">
-        <v>153</v>
-      </c>
-      <c r="B25" s="84">
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="54" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="55">
         <v>1250</v>
       </c>
-      <c r="C25" s="85" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="86" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="86"/>
-      <c r="C26" s="86"/>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="83" t="s">
-        <v>155</v>
-      </c>
-      <c r="B27" s="87">
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="82" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="82"/>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="54" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="56">
         <f>IF(B24=0,"Ugyldig: startverdi er 0",(B25-B24)/B24*100)</f>
         <v>25</v>
       </c>
-      <c r="C27" s="85" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="83" t="s">
-        <v>143</v>
-      </c>
-      <c r="B28" s="88">
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="54" t="s">
+        <v>122</v>
+      </c>
+      <c r="B28" s="57">
         <f>B25-B24</f>
         <v>250</v>
       </c>
-      <c r="C28" s="85" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="83" t="s">
-        <v>157</v>
-      </c>
-      <c r="B29" s="89" t="str">
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="B29" s="58" t="str">
         <f>IF(ISNUMBER(B27),TEXT(B27,"0.00")&amp;" %",B27)</f>
         <v>25.00 %</v>
       </c>
-      <c r="C29" s="85" t="s">
-        <v>158</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="A16:C16"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4346,359 +4546,359 @@
   <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="18" style="37" customWidth="1"/>
-    <col min="2" max="2" width="15" style="37" customWidth="1"/>
-    <col min="3" max="3" width="18" style="37" customWidth="1"/>
-    <col min="4" max="4" width="15" style="37" customWidth="1"/>
-    <col min="5" max="16384" width="8.6640625" style="37"/>
+    <col min="1" max="1" width="18" style="20" customWidth="1"/>
+    <col min="2" max="2" width="15" style="20" customWidth="1"/>
+    <col min="3" max="3" width="18" style="20" customWidth="1"/>
+    <col min="4" max="4" width="15" style="20" customWidth="1"/>
+    <col min="5" max="16384" width="8.6640625" style="20"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="42" t="s">
+      <c r="A1" s="73" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" s="73"/>
+      <c r="C1" s="73"/>
+      <c r="D1" s="73"/>
+    </row>
+    <row r="3" spans="1:4" ht="19.5" customHeight="1">
+      <c r="A3" s="72" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="72"/>
+      <c r="C3" s="72"/>
+      <c r="D3" s="72"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="22"/>
+      <c r="C4" s="23">
+        <f>B4/1000000</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="42"/>
-      <c r="C1" s="42"/>
-      <c r="D1" s="42"/>
-    </row>
-    <row r="3" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A3" s="44" t="s">
+      <c r="B5" s="22"/>
+      <c r="C5" s="23">
+        <f>B5*1000000</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="38" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="39"/>
-      <c r="C4" s="40">
-        <f>B4/1000000</f>
-        <v>0</v>
-      </c>
-      <c r="D4" s="41" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="23">
+        <f>B6/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="24" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="38" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="40">
-        <f>B5*1000000</f>
-        <v>0</v>
-      </c>
-      <c r="D5" s="41" t="s">
+      <c r="B7" s="22"/>
+      <c r="C7" s="23">
+        <f>B7*1000</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="24" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="21" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="38" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="23">
+        <f>B8/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40">
-        <f>B6/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D6" s="41" t="s">
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="21" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="38" t="s">
+      <c r="B9" s="22"/>
+      <c r="C9" s="23">
+        <f>B9/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40">
-        <f>B7*1000</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="41" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="38" t="s">
+    </row>
+    <row r="11" spans="1:4" ht="19.5" customHeight="1">
+      <c r="A11" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40">
-        <f>B8/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="41" t="s">
+      <c r="B11" s="72"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="21" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="38" t="s">
+      <c r="B12" s="22"/>
+      <c r="C12" s="23">
+        <f>B12/10</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="39"/>
-      <c r="C9" s="40">
-        <f>B9/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="41" t="s">
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="21" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A11" s="44" t="s">
+      <c r="B13" s="22"/>
+      <c r="C13" s="23">
+        <f>B13/100</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="44"/>
-      <c r="C11" s="44"/>
-      <c r="D11" s="44"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="38" t="s">
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40">
-        <f>B12/10</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="41" t="s">
+      <c r="B14" s="22"/>
+      <c r="C14" s="23">
+        <f>B14/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="21" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="38" t="s">
+      <c r="B15" s="22"/>
+      <c r="C15" s="23">
+        <f>B15/1000</f>
+        <v>0</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="40">
-        <f>B13/100</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="41" t="s">
+      <c r="B16" s="22"/>
+      <c r="C16" s="23">
+        <f>B16*1000</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="38" t="s">
+    <row r="17" spans="1:4">
+      <c r="A17" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="40">
-        <f>B14/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D14" s="41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="38" t="s">
+      <c r="B17" s="22"/>
+      <c r="C17" s="23">
+        <f>B17*100</f>
+        <v>0</v>
+      </c>
+      <c r="D17" s="24" t="s">
         <v>71</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40">
-        <f>B15/1000</f>
-        <v>0</v>
-      </c>
-      <c r="D15" s="41" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="38" t="s">
+    </row>
+    <row r="19" spans="1:4" ht="19.5" customHeight="1">
+      <c r="A19" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40">
-        <f>B16*1000</f>
-        <v>0</v>
-      </c>
-      <c r="D16" s="41" t="s">
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="21" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="38" t="s">
+      <c r="B20" s="22"/>
+      <c r="C20" s="23">
+        <f>B20/100</f>
+        <v>0</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40">
-        <f>B17*100</f>
-        <v>0</v>
-      </c>
-      <c r="D17" s="41" t="s">
+      <c r="B21" s="22"/>
+      <c r="C21" s="23">
+        <f>B21/10000</f>
+        <v>0</v>
+      </c>
+      <c r="D21" s="24" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A19" s="44" t="s">
+    <row r="22" spans="1:4">
+      <c r="A22" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="38" t="s">
+      <c r="B22" s="22"/>
+      <c r="C22" s="23">
+        <f>B22/1000000</f>
+        <v>0</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40">
-        <f>B20/100</f>
-        <v>0</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="38" t="s">
+      <c r="B23" s="22"/>
+      <c r="C23" s="23">
+        <f>B23*10000</f>
+        <v>0</v>
+      </c>
+      <c r="D23" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40">
-        <f>B21/10000</f>
-        <v>0</v>
-      </c>
-      <c r="D21" s="41" t="s">
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="21" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="38" t="s">
+      <c r="B24" s="22"/>
+      <c r="C24" s="23">
+        <f>B24*1000000</f>
+        <v>0</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40">
-        <f>B22/1000000</f>
-        <v>0</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="38" t="s">
+      <c r="B25" s="22"/>
+      <c r="C25" s="23">
+        <f>B25*1000</f>
+        <v>0</v>
+      </c>
+      <c r="D25" s="24" t="s">
         <v>81</v>
-      </c>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40">
-        <f>B23*10000</f>
-        <v>0</v>
-      </c>
-      <c r="D23" s="41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40">
-        <f>B24*1000000</f>
-        <v>0</v>
-      </c>
-      <c r="D24" s="41" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" s="39"/>
-      <c r="C25" s="40">
-        <f>B25*1000</f>
-        <v>0</v>
-      </c>
-      <c r="D25" s="41" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="19.5" customHeight="1"/>
     <row r="28" spans="1:4" ht="15.6">
-      <c r="A28" s="44" t="s">
+      <c r="A28" s="72" t="s">
+        <v>82</v>
+      </c>
+      <c r="B28" s="72"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" s="22"/>
+      <c r="C29" s="23">
+        <f>B29*3.6</f>
+        <v>0</v>
+      </c>
+      <c r="D29" s="24" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B30" s="22"/>
+      <c r="C30" s="23">
+        <f>B30/3.6</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" s="38" t="s">
+    </row>
+    <row r="32" spans="1:4" ht="15.6">
+      <c r="A32" s="72" t="s">
         <v>87</v>
       </c>
-      <c r="B29" s="39"/>
-      <c r="C29" s="40">
-        <f>B29*3.6</f>
-        <v>0</v>
-      </c>
-      <c r="D29" s="41" t="s">
+      <c r="B32" s="72"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="21" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="40">
-        <f>B30/3.6</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="41" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" ht="15.6">
-      <c r="A32" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B32" s="44"/>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" s="38" t="s">
-        <v>92</v>
-      </c>
-      <c r="B33" s="39"/>
-      <c r="C33" s="40">
+      <c r="B33" s="22"/>
+      <c r="C33" s="23">
         <f>B33*9/5+32</f>
         <v>32</v>
       </c>
-      <c r="D33" s="41" t="s">
-        <v>93</v>
+      <c r="D33" s="24" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="38" t="s">
-        <v>94</v>
-      </c>
-      <c r="B34" s="39"/>
-      <c r="C34" s="40">
+      <c r="A34" s="21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B34" s="22"/>
+      <c r="C34" s="23">
         <f>(B34-32)*5/9</f>
         <v>-17.777777777777779</v>
       </c>
-      <c r="D34" s="41" t="s">
-        <v>95</v>
+      <c r="D34" s="24" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A35" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="B35" s="39"/>
-      <c r="C35" s="40">
+      <c r="A35" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="23">
         <f>B35+273.15</f>
         <v>273.14999999999998</v>
       </c>
-      <c r="D35" s="41" t="s">
-        <v>97</v>
+      <c r="D35" s="24" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="19.5" customHeight="1"/>
@@ -4739,753 +4939,753 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="A1" s="74" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="H3" s="7" t="b">
+      <c r="B3" s="2"/>
+      <c r="H3" s="3" t="b">
         <f>AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;"")</f>
         <v>0</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K3" s="76" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="2"/>
+      <c r="L3" s="76"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L4" s="9" t="str">
+      <c r="L4" s="5" t="str">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),SUM(C8:C27),"")</f>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:12" ht="27.75" customHeight="1">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="9" t="str">
+      <c r="L5" s="5" t="str">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),(SUM(C8:C27)+1)/2,"")</f>
         <v/>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1">
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="9" t="str">
+      <c r="L6" s="5" t="str">
         <f ca="1">IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),OFFSET(A8,COUNT(G8:G27),0)+(L5-IF(COUNT(G8:G27)&gt;0,OFFSET(F8,COUNT(G8:G27)-1,0),0))/OFFSET(C8,COUNT(G8:G27),0)*OFFSET(H8,COUNT(G8:G27),0),"")</f>
         <v/>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1">
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="9" t="str">
+      <c r="L7" s="5" t="str">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),SUM(E8:E27)/SUM(C8:C27),"")</f>
         <v/>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" s="11" t="str">
+      <c r="A8" s="2"/>
+      <c r="B8" s="7" t="str">
         <f t="shared" ref="B8:B27" si="0">IF(A8="","",IF(A9="",B$3,A9))</f>
         <v/>
       </c>
-      <c r="C8" s="6"/>
-      <c r="D8" s="11" t="str">
+      <c r="C8" s="2"/>
+      <c r="D8" s="7" t="str">
         <f t="shared" ref="D8:D27" si="1">IF(A8&lt;&gt;"",(A8+B8)/2,"")</f>
         <v/>
       </c>
-      <c r="E8" s="11" t="str">
+      <c r="E8" s="7" t="str">
         <f t="shared" ref="E8:E27" si="2">IF(A8&lt;&gt;"",C8*D8,"")</f>
         <v/>
       </c>
-      <c r="F8" s="11" t="str">
+      <c r="F8" s="7" t="str">
         <f>IF(C8&lt;&gt;"",C8,"")</f>
         <v/>
       </c>
-      <c r="G8" s="11" t="str">
+      <c r="G8" s="7" t="str">
         <f>IF(AND(F8&lt;&gt;"",F8&lt;J8,H3),F8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="11" t="str">
+      <c r="H8" s="7" t="str">
         <f t="shared" ref="H8:H27" si="3">IF(A8&lt;&gt;"",(B8-A8),"")</f>
         <v/>
       </c>
-      <c r="I8" s="11" t="str">
+      <c r="I8" s="7" t="str">
         <f t="shared" ref="I8:I27" si="4">IF(AND(A8&lt;&gt;"",H8&lt;&gt;"",H8&lt;&gt;0),C8/H8,"")</f>
         <v/>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="3">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),(IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),SUM(C8:C27),1)+1)/2,0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="1" t="str">
+      <c r="K8" s="77" t="str">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),"✅ Klar – se Histogram-fanen","⚠️ Fyll inn data i kolonne A og C")</f>
         <v>⚠️ Fyll inn data i kolonne A og C</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="77"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" s="11" t="str">
+      <c r="A9" s="2"/>
+      <c r="B9" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C9" s="6"/>
-      <c r="D9" s="11" t="str">
+      <c r="C9" s="2"/>
+      <c r="D9" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E9" s="11" t="str">
+      <c r="E9" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F9" s="11" t="str">
+      <c r="F9" s="7" t="str">
         <f t="shared" ref="F9:F27" si="5">IF(C9&lt;&gt;"",F8+C9,"")</f>
         <v/>
       </c>
-      <c r="G9" s="11" t="str">
+      <c r="G9" s="7" t="str">
         <f>IF(AND(F9&lt;&gt;"",F9&lt;J8,H3),F9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="11" t="str">
+      <c r="H9" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I9" s="11" t="str">
+      <c r="I9" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" s="11" t="str">
+      <c r="A10" s="2"/>
+      <c r="B10" s="7" t="str">
         <f>IF(A10="","",IF(A11="",B$3,A11))</f>
         <v/>
       </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="11" t="str">
+      <c r="C10" s="2"/>
+      <c r="D10" s="7" t="str">
         <f>IF(A10&lt;&gt;"",(A10+B10)/2,"")</f>
         <v/>
       </c>
-      <c r="E10" s="11" t="str">
+      <c r="E10" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F10" s="11" t="str">
+      <c r="F10" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G10" s="11" t="str">
+      <c r="G10" s="7" t="str">
         <f>IF(AND(F10&lt;&gt;"",F10&lt;J8,H3),F10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="11" t="str">
+      <c r="H10" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I10" s="11" t="str">
+      <c r="I10" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" s="11" t="str">
+      <c r="A11" s="2"/>
+      <c r="B11" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="11" t="str">
+      <c r="C11" s="2"/>
+      <c r="D11" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E11" s="11" t="str">
+      <c r="E11" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F11" s="11" t="str">
+      <c r="F11" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G11" s="11" t="str">
+      <c r="G11" s="7" t="str">
         <f>IF(AND(F11&lt;&gt;"",F11&lt;J8,H3),F11,"")</f>
         <v/>
       </c>
-      <c r="H11" s="11" t="str">
+      <c r="H11" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I11" s="11" t="str">
+      <c r="I11" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" s="11" t="str">
+      <c r="A12" s="2"/>
+      <c r="B12" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="11" t="str">
+      <c r="C12" s="2"/>
+      <c r="D12" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E12" s="11" t="str">
+      <c r="E12" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F12" s="11" t="str">
+      <c r="F12" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G12" s="11" t="str">
+      <c r="G12" s="7" t="str">
         <f>IF(AND(F12&lt;&gt;"",F12&lt;J8,H3),F12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="11" t="str">
+      <c r="H12" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I12" s="11" t="str">
+      <c r="I12" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" s="11" t="str">
+      <c r="A13" s="2"/>
+      <c r="B13" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="11" t="str">
+      <c r="C13" s="2"/>
+      <c r="D13" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E13" s="11" t="str">
+      <c r="E13" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F13" s="11" t="str">
+      <c r="F13" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G13" s="11" t="str">
+      <c r="G13" s="7" t="str">
         <f>IF(AND(F13&lt;&gt;"",F13&lt;J8,H3),F13,"")</f>
         <v/>
       </c>
-      <c r="H13" s="11" t="str">
+      <c r="H13" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I13" s="11" t="str">
+      <c r="I13" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" s="11" t="str">
+      <c r="A14" s="2"/>
+      <c r="B14" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C14" s="6"/>
-      <c r="D14" s="11" t="str">
+      <c r="C14" s="2"/>
+      <c r="D14" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E14" s="11" t="str">
+      <c r="E14" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F14" s="11" t="str">
+      <c r="F14" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G14" s="11" t="str">
+      <c r="G14" s="7" t="str">
         <f>IF(AND(F14&lt;&gt;"",F14&lt;J8,H3),F14,"")</f>
         <v/>
       </c>
-      <c r="H14" s="11" t="str">
+      <c r="H14" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I14" s="11" t="str">
+      <c r="I14" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" s="11" t="str">
+      <c r="A15" s="2"/>
+      <c r="B15" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C15" s="6"/>
-      <c r="D15" s="11" t="str">
+      <c r="C15" s="2"/>
+      <c r="D15" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E15" s="11" t="str">
+      <c r="E15" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F15" s="11" t="str">
+      <c r="F15" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G15" s="11" t="str">
+      <c r="G15" s="7" t="str">
         <f>IF(AND(F15&lt;&gt;"",F15&lt;J8,H3),F15,"")</f>
         <v/>
       </c>
-      <c r="H15" s="11" t="str">
+      <c r="H15" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I15" s="11" t="str">
+      <c r="I15" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" s="11" t="str">
+      <c r="A16" s="2"/>
+      <c r="B16" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C16" s="6"/>
-      <c r="D16" s="11" t="str">
+      <c r="C16" s="2"/>
+      <c r="D16" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E16" s="11" t="str">
+      <c r="E16" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F16" s="11" t="str">
+      <c r="F16" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G16" s="11" t="str">
+      <c r="G16" s="7" t="str">
         <f>IF(AND(F16&lt;&gt;"",F16&lt;J8,H3),F16,"")</f>
         <v/>
       </c>
-      <c r="H16" s="11" t="str">
+      <c r="H16" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I16" s="11" t="str">
+      <c r="I16" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" s="11" t="str">
+      <c r="A17" s="2"/>
+      <c r="B17" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C17" s="6"/>
-      <c r="D17" s="11" t="str">
+      <c r="C17" s="2"/>
+      <c r="D17" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E17" s="11" t="str">
+      <c r="E17" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F17" s="11" t="str">
+      <c r="F17" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G17" s="11" t="str">
+      <c r="G17" s="7" t="str">
         <f>IF(AND(F17&lt;&gt;"",F17&lt;J8,H3),F17,"")</f>
         <v/>
       </c>
-      <c r="H17" s="11" t="str">
+      <c r="H17" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I17" s="11" t="str">
+      <c r="I17" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" s="11" t="str">
+      <c r="A18" s="2"/>
+      <c r="B18" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C18" s="6"/>
-      <c r="D18" s="11" t="str">
+      <c r="C18" s="2"/>
+      <c r="D18" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E18" s="11" t="str">
+      <c r="E18" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F18" s="11" t="str">
+      <c r="F18" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G18" s="11" t="str">
+      <c r="G18" s="7" t="str">
         <f>IF(AND(F18&lt;&gt;"",F18&lt;J8,H3),F18,"")</f>
         <v/>
       </c>
-      <c r="H18" s="11" t="str">
+      <c r="H18" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I18" s="11" t="str">
+      <c r="I18" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" s="11" t="str">
+      <c r="A19" s="2"/>
+      <c r="B19" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="11" t="str">
+      <c r="C19" s="2"/>
+      <c r="D19" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E19" s="11" t="str">
+      <c r="E19" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F19" s="11" t="str">
+      <c r="F19" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G19" s="11" t="str">
+      <c r="G19" s="7" t="str">
         <f>IF(AND(F19&lt;&gt;"",F19&lt;J8,H3),F19,"")</f>
         <v/>
       </c>
-      <c r="H19" s="11" t="str">
+      <c r="H19" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I19" s="11" t="str">
+      <c r="I19" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" s="11" t="str">
+      <c r="A20" s="2"/>
+      <c r="B20" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="11" t="str">
+      <c r="C20" s="2"/>
+      <c r="D20" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E20" s="11" t="str">
+      <c r="E20" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F20" s="11" t="str">
+      <c r="F20" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G20" s="11" t="str">
+      <c r="G20" s="7" t="str">
         <f>IF(AND(F20&lt;&gt;"",F20&lt;J8,H3),F20,"")</f>
         <v/>
       </c>
-      <c r="H20" s="11" t="str">
+      <c r="H20" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I20" s="11" t="str">
+      <c r="I20" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" s="11" t="str">
+      <c r="A21" s="2"/>
+      <c r="B21" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="11" t="str">
+      <c r="C21" s="2"/>
+      <c r="D21" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E21" s="11" t="str">
+      <c r="E21" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F21" s="11" t="str">
+      <c r="F21" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G21" s="11" t="str">
+      <c r="G21" s="7" t="str">
         <f>IF(AND(F21&lt;&gt;"",F21&lt;J8,H3),F21,"")</f>
         <v/>
       </c>
-      <c r="H21" s="11" t="str">
+      <c r="H21" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I21" s="11" t="str">
+      <c r="I21" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:9" ht="15" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" s="11" t="str">
+      <c r="A22" s="2"/>
+      <c r="B22" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="11" t="str">
+      <c r="C22" s="2"/>
+      <c r="D22" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E22" s="11" t="str">
+      <c r="E22" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F22" s="11" t="str">
+      <c r="F22" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G22" s="11" t="str">
+      <c r="G22" s="7" t="str">
         <f>IF(AND(F22&lt;&gt;"",F22&lt;J8,H3),F22,"")</f>
         <v/>
       </c>
-      <c r="H22" s="11" t="str">
+      <c r="H22" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I22" s="11" t="str">
+      <c r="I22" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:9" ht="15" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" s="11" t="str">
+      <c r="A23" s="2"/>
+      <c r="B23" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="11" t="str">
+      <c r="C23" s="2"/>
+      <c r="D23" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E23" s="11" t="str">
+      <c r="E23" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F23" s="11" t="str">
+      <c r="F23" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G23" s="11" t="str">
+      <c r="G23" s="7" t="str">
         <f>IF(AND(F23&lt;&gt;"",F23&lt;J8,H3),F23,"")</f>
         <v/>
       </c>
-      <c r="H23" s="11" t="str">
+      <c r="H23" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I23" s="11" t="str">
+      <c r="I23" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:9" ht="15" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" s="11" t="str">
+      <c r="A24" s="2"/>
+      <c r="B24" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="11" t="str">
+      <c r="C24" s="2"/>
+      <c r="D24" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E24" s="11" t="str">
+      <c r="E24" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F24" s="11" t="str">
+      <c r="F24" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G24" s="11" t="str">
+      <c r="G24" s="7" t="str">
         <f>IF(AND(F24&lt;&gt;"",F24&lt;J8,H3),F24,"")</f>
         <v/>
       </c>
-      <c r="H24" s="11" t="str">
+      <c r="H24" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I24" s="11" t="str">
+      <c r="I24" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" s="11" t="str">
+      <c r="A25" s="2"/>
+      <c r="B25" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="11" t="str">
+      <c r="C25" s="2"/>
+      <c r="D25" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E25" s="11" t="str">
+      <c r="E25" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F25" s="11" t="str">
+      <c r="F25" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G25" s="11" t="str">
+      <c r="G25" s="7" t="str">
         <f>IF(AND(F25&lt;&gt;"",F25&lt;J8,H3),F25,"")</f>
         <v/>
       </c>
-      <c r="H25" s="11" t="str">
+      <c r="H25" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I25" s="11" t="str">
+      <c r="I25" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:9" ht="15" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" s="11" t="str">
+      <c r="A26" s="2"/>
+      <c r="B26" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="11" t="str">
+      <c r="C26" s="2"/>
+      <c r="D26" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E26" s="11" t="str">
+      <c r="E26" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F26" s="11" t="str">
+      <c r="F26" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G26" s="11" t="str">
+      <c r="G26" s="7" t="str">
         <f>IF(AND(F26&lt;&gt;"",F26&lt;J8,H3),F26,"")</f>
         <v/>
       </c>
-      <c r="H26" s="11" t="str">
+      <c r="H26" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I26" s="11" t="str">
+      <c r="I26" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:9" ht="15" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" s="11" t="str">
+      <c r="A27" s="2"/>
+      <c r="B27" s="7" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="11" t="str">
+      <c r="C27" s="2"/>
+      <c r="D27" s="7" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E27" s="11" t="str">
+      <c r="E27" s="7" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="F27" s="11" t="str">
+      <c r="F27" s="7" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="G27" s="11" t="str">
+      <c r="G27" s="7" t="str">
         <f>IF(AND(F27&lt;&gt;"",F27&lt;J8,H3),F27,"")</f>
         <v/>
       </c>
-      <c r="H27" s="11" t="str">
+      <c r="H27" s="7" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="I27" s="11" t="str">
+      <c r="I27" s="7" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -5514,10 +5714,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="8" t="s">
         <v>13</v>
       </c>
     </row>

--- a/SnorresMatteskjema.xlsx
+++ b/SnorresMatteskjema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45B0BB9A-9538-4C81-8386-084127CF1B78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B4C362-27B2-4773-BD5D-F08FA95CF84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="501" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,7 +750,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -955,6 +955,18 @@
         <bgColor rgb="FF666699"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFFCC"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1164,18 +1176,31 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="15" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="15" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1188,6 +1213,21 @@
     <xf numFmtId="0" fontId="17" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1197,21 +1237,6 @@
     <xf numFmtId="0" fontId="24" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1230,24 +1255,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="35" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="15" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1327,10 +1341,10 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFCCFFCC"/>
       <color rgb="FF373A4B"/>
       <color rgb="FF1FBB96"/>
       <color rgb="FF2EC4A1"/>
-      <color rgb="FFCCFFCC"/>
       <color rgb="FFCCCCFF"/>
       <color rgb="FFFFCCCC"/>
       <color rgb="FF2E3047"/>
@@ -2942,7 +2956,7 @@
   <sheetPr>
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="22.77734375" customWidth="1"/>
@@ -2954,842 +2968,834 @@
     <col min="7" max="7" width="17.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="25.2" customHeight="1">
-      <c r="A1" s="85" t="s">
+    <row r="1" spans="1:7" ht="19.2" customHeight="1">
+      <c r="A1" s="64" t="s">
         <v>138</v>
       </c>
-      <c r="B1" s="85"/>
-      <c r="C1" s="85"/>
-      <c r="D1" s="85"/>
-      <c r="E1" s="85"/>
-    </row>
-    <row r="2" spans="1:7" ht="19.2" customHeight="1">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="10">
+        <v>2500000</v>
+      </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="10">
-        <v>2500000</v>
+        <v>135</v>
+      </c>
+      <c r="B3" s="11">
+        <v>0.33</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="9" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" s="11">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="9" t="s">
         <v>136</v>
       </c>
+      <c r="B4" s="12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="21" customHeight="1">
+      <c r="A5" s="60" t="s">
+        <v>133</v>
+      </c>
       <c r="B5" s="12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="15.6" customHeight="1">
+      <c r="A6" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="12">
+        <v>13385</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="14.4" customHeight="1"/>
+    <row r="8" spans="1:7" ht="21.75" customHeight="1">
+      <c r="A8" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="42" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="21" customHeight="1">
-      <c r="A6" s="80" t="s">
-        <v>133</v>
-      </c>
-      <c r="B6" s="12">
+      <c r="C8" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="59">
+        <v>0</v>
+      </c>
+      <c r="B9" s="58">
+        <f>B2</f>
+        <v>2500000</v>
+      </c>
+      <c r="C9" s="15">
+        <f>$B$5</f>
         <v>50</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="12">
+      <c r="D9" s="15">
+        <f>B9*B3%</f>
+        <v>8250</v>
+      </c>
+      <c r="E9" s="15">
+        <f>F9-C9-D9</f>
+        <v>5085</v>
+      </c>
+      <c r="F9" s="15">
+        <f>$B$6</f>
         <v>13385</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="6" customHeight="1"/>
-    <row r="9" spans="1:7" ht="21.75" customHeight="1">
-      <c r="A9" s="42" t="s">
+      <c r="G9" s="58">
+        <f>D9+E9</f>
+        <v>13335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="59">
+        <v>1</v>
+      </c>
+      <c r="B10" s="58">
+        <f t="shared" ref="B10:B33" si="0">B9-E9</f>
+        <v>2494915</v>
+      </c>
+      <c r="C10" s="15">
+        <f>$B$5</f>
+        <v>50</v>
+      </c>
+      <c r="D10" s="58">
+        <f t="shared" ref="D10:D33" si="1">B10*$B$3%</f>
+        <v>8233.2194999999992</v>
+      </c>
+      <c r="E10" s="15">
+        <f t="shared" ref="E10:E32" si="2">F10-C10-D10</f>
+        <v>5101.7805000000008</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" ref="F10:F33" si="3">$B$6</f>
+        <v>13385</v>
+      </c>
+      <c r="G10" s="58">
+        <f t="shared" ref="G10:G33" si="4">IFERROR(IF(OR(B10="",D10="",E10=""),0,MAX(0,B10+D10-E10)),"")</f>
+        <v>2498046.4390000002</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="59">
+        <v>2</v>
+      </c>
+      <c r="B11" s="58">
+        <f t="shared" si="0"/>
+        <v>2489813.2195000001</v>
+      </c>
+      <c r="C11" s="15">
+        <f t="shared" ref="C11:C33" si="5">$B$5</f>
+        <v>50</v>
+      </c>
+      <c r="D11" s="58">
+        <f t="shared" si="1"/>
+        <v>8216.3836243500009</v>
+      </c>
+      <c r="E11" s="15">
+        <f t="shared" si="2"/>
+        <v>5118.6163756499991</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G11" s="58">
+        <f t="shared" si="4"/>
+        <v>2492910.9867487005</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="59">
+        <v>3</v>
+      </c>
+      <c r="B12" s="58">
+        <f t="shared" si="0"/>
+        <v>2484694.6031243503</v>
+      </c>
+      <c r="C12" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D12" s="58">
+        <f t="shared" si="1"/>
+        <v>8199.4921903103568</v>
+      </c>
+      <c r="E12" s="15">
+        <f t="shared" si="2"/>
+        <v>5135.5078096896432</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G12" s="58">
+        <f t="shared" si="4"/>
+        <v>2487758.5875049708</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="59">
+        <v>4</v>
+      </c>
+      <c r="B13" s="58">
+        <f t="shared" si="0"/>
+        <v>2479559.0953146606</v>
+      </c>
+      <c r="C13" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D13" s="58">
+        <f t="shared" si="1"/>
+        <v>8182.5450145383802</v>
+      </c>
+      <c r="E13" s="15">
+        <f t="shared" si="2"/>
+        <v>5152.4549854616198</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G13" s="58">
+        <f t="shared" si="4"/>
+        <v>2482589.1853437372</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="59">
+        <v>5</v>
+      </c>
+      <c r="B14" s="58">
+        <f t="shared" si="0"/>
+        <v>2474406.6403291989</v>
+      </c>
+      <c r="C14" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D14" s="58">
+        <f t="shared" si="1"/>
+        <v>8165.5419130863565</v>
+      </c>
+      <c r="E14" s="15">
+        <f t="shared" si="2"/>
+        <v>5169.4580869136435</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G14" s="58">
+        <f t="shared" si="4"/>
+        <v>2477402.724155372</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="59">
+        <v>6</v>
+      </c>
+      <c r="B15" s="58">
+        <f t="shared" si="0"/>
+        <v>2469237.1822422855</v>
+      </c>
+      <c r="C15" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D15" s="58">
+        <f t="shared" si="1"/>
+        <v>8148.4827013995418</v>
+      </c>
+      <c r="E15" s="15">
+        <f t="shared" si="2"/>
+        <v>5186.5172986004582</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G15" s="58">
+        <f t="shared" si="4"/>
+        <v>2472199.1476450842</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="59">
+        <v>7</v>
+      </c>
+      <c r="B16" s="58">
+        <f t="shared" si="0"/>
+        <v>2464050.6649436848</v>
+      </c>
+      <c r="C16" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D16" s="58">
+        <f t="shared" si="1"/>
+        <v>8131.3671943141599</v>
+      </c>
+      <c r="E16" s="15">
+        <f t="shared" si="2"/>
+        <v>5203.6328056858401</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G16" s="58">
+        <f t="shared" si="4"/>
+        <v>2466978.3993323129</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="59">
+        <v>8</v>
+      </c>
+      <c r="B17" s="58">
+        <f t="shared" si="0"/>
+        <v>2458847.0321379988</v>
+      </c>
+      <c r="C17" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D17" s="58">
+        <f t="shared" si="1"/>
+        <v>8114.1952060553958</v>
+      </c>
+      <c r="E17" s="15">
+        <f t="shared" si="2"/>
+        <v>5220.8047939446042</v>
+      </c>
+      <c r="F17" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G17" s="58">
+        <f t="shared" si="4"/>
+        <v>2461740.4225501097</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="59">
+        <v>9</v>
+      </c>
+      <c r="B18" s="58">
+        <f t="shared" si="0"/>
+        <v>2453626.2273440543</v>
+      </c>
+      <c r="C18" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D18" s="58">
+        <f t="shared" si="1"/>
+        <v>8096.9665502353791</v>
+      </c>
+      <c r="E18" s="15">
+        <f t="shared" si="2"/>
+        <v>5238.0334497646209</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G18" s="58">
+        <f t="shared" si="4"/>
+        <v>2456485.1604445246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="59">
+        <v>10</v>
+      </c>
+      <c r="B19" s="58">
+        <f t="shared" si="0"/>
+        <v>2448388.1938942894</v>
+      </c>
+      <c r="C19" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D19" s="58">
+        <f t="shared" si="1"/>
+        <v>8079.6810398511552</v>
+      </c>
+      <c r="E19" s="15">
+        <f t="shared" si="2"/>
+        <v>5255.3189601488448</v>
+      </c>
+      <c r="F19" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G19" s="58">
+        <f t="shared" si="4"/>
+        <v>2451212.5559739918</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="59">
+        <v>11</v>
+      </c>
+      <c r="B20" s="58">
+        <f t="shared" si="0"/>
+        <v>2443132.8749341406</v>
+      </c>
+      <c r="C20" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D20" s="58">
+        <f t="shared" si="1"/>
+        <v>8062.3384872826637</v>
+      </c>
+      <c r="E20" s="15">
+        <f t="shared" si="2"/>
+        <v>5272.6615127173363</v>
+      </c>
+      <c r="F20" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G20" s="58">
+        <f t="shared" si="4"/>
+        <v>2445922.5519087063</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="59">
+        <v>12</v>
+      </c>
+      <c r="B21" s="58">
+        <f t="shared" si="0"/>
+        <v>2437860.2134214235</v>
+      </c>
+      <c r="C21" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D21" s="58">
+        <f t="shared" si="1"/>
+        <v>8044.9387042906974</v>
+      </c>
+      <c r="E21" s="15">
+        <f t="shared" si="2"/>
+        <v>5290.0612957093026</v>
+      </c>
+      <c r="F21" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G21" s="58">
+        <f t="shared" si="4"/>
+        <v>2440615.0908300052</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="59">
+        <v>13</v>
+      </c>
+      <c r="B22" s="58">
+        <f t="shared" si="0"/>
+        <v>2432570.1521257143</v>
+      </c>
+      <c r="C22" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D22" s="58">
+        <f t="shared" si="1"/>
+        <v>8027.4815020148571</v>
+      </c>
+      <c r="E22" s="15">
+        <f t="shared" si="2"/>
+        <v>5307.5184979851429</v>
+      </c>
+      <c r="F22" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G22" s="58">
+        <f t="shared" si="4"/>
+        <v>2435290.1151297437</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="59">
+        <v>14</v>
+      </c>
+      <c r="B23" s="15">
+        <f t="shared" si="0"/>
+        <v>2427262.633627729</v>
+      </c>
+      <c r="C23" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D23" s="58">
+        <f t="shared" si="1"/>
+        <v>8009.9666909715061</v>
+      </c>
+      <c r="E23" s="15">
+        <f t="shared" si="2"/>
+        <v>5325.0333090284939</v>
+      </c>
+      <c r="F23" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G23" s="15">
+        <f t="shared" si="4"/>
+        <v>2429947.5670096721</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="59">
+        <v>15</v>
+      </c>
+      <c r="B24" s="15">
+        <f t="shared" si="0"/>
+        <v>2421937.6003187005</v>
+      </c>
+      <c r="C24" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D24" s="58">
+        <f t="shared" si="1"/>
+        <v>7992.3940810517115</v>
+      </c>
+      <c r="E24" s="15">
+        <f t="shared" si="2"/>
+        <v>5342.6059189482885</v>
+      </c>
+      <c r="F24" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G24" s="15">
+        <f t="shared" si="4"/>
+        <v>2424587.3884808044</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" customHeight="1">
+      <c r="A25" s="59">
+        <v>16</v>
+      </c>
+      <c r="B25" s="15">
+        <f t="shared" si="0"/>
+        <v>2416594.9943997525</v>
+      </c>
+      <c r="C25" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D25" s="58">
+        <f t="shared" si="1"/>
+        <v>7974.7634815191832</v>
+      </c>
+      <c r="E25" s="15">
+        <f t="shared" si="2"/>
+        <v>5360.2365184808168</v>
+      </c>
+      <c r="F25" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G25" s="15">
+        <f t="shared" si="4"/>
+        <v>2419209.5213627908</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="59">
+        <v>17</v>
+      </c>
+      <c r="B26" s="15">
+        <f t="shared" si="0"/>
+        <v>2411234.7578812717</v>
+      </c>
+      <c r="C26" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D26" s="58">
+        <f t="shared" si="1"/>
+        <v>7957.0747010081968</v>
+      </c>
+      <c r="E26" s="15">
+        <f t="shared" si="2"/>
+        <v>5377.9252989918032</v>
+      </c>
+      <c r="F26" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G26" s="15">
+        <f t="shared" si="4"/>
+        <v>2413813.9072832884</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="59">
+        <v>18</v>
+      </c>
+      <c r="B27" s="15">
+        <f t="shared" si="0"/>
+        <v>2405856.83258228</v>
+      </c>
+      <c r="C27" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D27" s="58">
+        <f t="shared" si="1"/>
+        <v>7939.3275475215241</v>
+      </c>
+      <c r="E27" s="15">
+        <f t="shared" si="2"/>
+        <v>5395.6724524784759</v>
+      </c>
+      <c r="F27" s="15">
+        <f>$B$6</f>
+        <v>13385</v>
+      </c>
+      <c r="G27" s="15">
+        <f t="shared" si="4"/>
+        <v>2408400.4876773227</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="59">
+        <v>19</v>
+      </c>
+      <c r="B28" s="15">
+        <f t="shared" si="0"/>
+        <v>2400461.1601298014</v>
+      </c>
+      <c r="C28" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D28" s="58">
+        <f t="shared" si="1"/>
+        <v>7921.5218284283446</v>
+      </c>
+      <c r="E28" s="15">
+        <f t="shared" si="2"/>
+        <v>5413.4781715716554</v>
+      </c>
+      <c r="F28" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G28" s="15">
+        <f t="shared" si="4"/>
+        <v>2402969.2037866581</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="59">
+        <v>20</v>
+      </c>
+      <c r="B29" s="15">
+        <f t="shared" si="0"/>
+        <v>2395047.6819582297</v>
+      </c>
+      <c r="C29" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D29" s="58">
+        <f t="shared" si="1"/>
+        <v>7903.6573504621583</v>
+      </c>
+      <c r="E29" s="15">
+        <f t="shared" si="2"/>
+        <v>5431.3426495378417</v>
+      </c>
+      <c r="F29" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G29" s="15">
+        <f t="shared" si="4"/>
+        <v>2397519.9966591536</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="59">
+        <v>21</v>
+      </c>
+      <c r="B30" s="15">
+        <f t="shared" si="0"/>
+        <v>2389616.3393086917</v>
+      </c>
+      <c r="C30" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D30" s="58">
+        <f t="shared" si="1"/>
+        <v>7885.733919718682</v>
+      </c>
+      <c r="E30" s="15">
+        <f>F30-C30-D30</f>
+        <v>5449.266080281318</v>
+      </c>
+      <c r="F30" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G30" s="15">
+        <f t="shared" si="4"/>
+        <v>2392052.8071481292</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="59">
+        <v>22</v>
+      </c>
+      <c r="B31" s="15">
+        <f t="shared" si="0"/>
+        <v>2384167.0732284104</v>
+      </c>
+      <c r="C31" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D31" s="58">
+        <f t="shared" si="1"/>
+        <v>7867.751341653754</v>
+      </c>
+      <c r="E31" s="15">
+        <f t="shared" si="2"/>
+        <v>5467.248658346246</v>
+      </c>
+      <c r="F31" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G31" s="15">
+        <f t="shared" si="4"/>
+        <v>2386567.5759117175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="59">
         <v>23</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="B32" s="15">
+        <f t="shared" si="0"/>
+        <v>2378699.824570064</v>
+      </c>
+      <c r="C32" s="15">
+        <f t="shared" si="5"/>
+        <v>50</v>
+      </c>
+      <c r="D32" s="58">
+        <f t="shared" si="1"/>
+        <v>7849.7094210812111</v>
+      </c>
+      <c r="E32" s="15">
+        <f t="shared" si="2"/>
+        <v>5485.2905789187889</v>
+      </c>
+      <c r="F32" s="15">
+        <f t="shared" si="3"/>
+        <v>13385</v>
+      </c>
+      <c r="G32" s="15">
+        <f t="shared" si="4"/>
+        <v>2381064.243412226</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="59">
         <v>24</v>
       </c>
-      <c r="C9" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="D9" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="42" t="s">
-        <v>137</v>
-      </c>
-      <c r="G9" s="42" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="79">
-        <v>0</v>
-      </c>
-      <c r="B10" s="78">
-        <f>B3</f>
-        <v>2500000</v>
-      </c>
-      <c r="C10" s="15">
-        <f>$B$6</f>
+      <c r="B33" s="15">
+        <f t="shared" si="0"/>
+        <v>2373214.533991145</v>
+      </c>
+      <c r="C33" s="15">
+        <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D10" s="15">
-        <f>B10*B4%</f>
-        <v>8250</v>
-      </c>
-      <c r="E10" s="15">
-        <f>F10-C10-D10</f>
-        <v>5085</v>
-      </c>
-      <c r="F10" s="15">
-        <f>$B$7</f>
+      <c r="D33" s="58">
+        <f t="shared" si="1"/>
+        <v>7831.6079621707786</v>
+      </c>
+      <c r="E33" s="15">
+        <f t="shared" ref="E33" si="6">F33-C33-D33</f>
+        <v>5503.3920378292214</v>
+      </c>
+      <c r="F33" s="15">
+        <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G10" s="78">
-        <f>D10+E10</f>
-        <v>13335</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="79">
-        <v>1</v>
-      </c>
-      <c r="B11" s="78">
-        <f>B10-E10</f>
-        <v>2494915</v>
-      </c>
-      <c r="C11" s="15">
-        <f>$B$6</f>
-        <v>50</v>
-      </c>
-      <c r="D11" s="78">
-        <f>B11*$B$4%</f>
-        <v>8233.2194999999992</v>
-      </c>
-      <c r="E11" s="15">
-        <f t="shared" ref="E11:E33" si="0">F11-C11-D11</f>
-        <v>5101.7805000000008</v>
-      </c>
-      <c r="F11" s="15">
-        <f t="shared" ref="F11:F34" si="1">$B$7</f>
-        <v>13385</v>
-      </c>
-      <c r="G11" s="78">
-        <f>IFERROR(IF(OR(B11="",D11="",E11=""),0,MAX(0,B11+D11-E11)),"")</f>
-        <v>2498046.4390000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="79">
-        <v>2</v>
-      </c>
-      <c r="B12" s="78">
-        <f>B11-E11</f>
-        <v>2489813.2195000001</v>
-      </c>
-      <c r="C12" s="15">
-        <f t="shared" ref="C12:C34" si="2">$B$6</f>
-        <v>50</v>
-      </c>
-      <c r="D12" s="78">
-        <f>B12*$B$4%</f>
-        <v>8216.3836243500009</v>
-      </c>
-      <c r="E12" s="15">
-        <f t="shared" si="0"/>
-        <v>5118.6163756499991</v>
-      </c>
-      <c r="F12" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G12" s="78">
-        <f>IFERROR(IF(OR(B12="",D12="",E12=""),0,MAX(0,B12+D12-E12)),"")</f>
-        <v>2492910.9867487005</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="79">
-        <v>3</v>
-      </c>
-      <c r="B13" s="78">
-        <f>B12-E12</f>
-        <v>2484694.6031243503</v>
-      </c>
-      <c r="C13" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D13" s="78">
-        <f>B13*$B$4%</f>
-        <v>8199.4921903103568</v>
-      </c>
-      <c r="E13" s="15">
-        <f t="shared" si="0"/>
-        <v>5135.5078096896432</v>
-      </c>
-      <c r="F13" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G13" s="78">
-        <f>IFERROR(IF(OR(B13="",D13="",E13=""),0,MAX(0,B13+D13-E13)),"")</f>
-        <v>2487758.5875049708</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="79">
-        <v>4</v>
-      </c>
-      <c r="B14" s="78">
-        <f>B13-E13</f>
-        <v>2479559.0953146606</v>
-      </c>
-      <c r="C14" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D14" s="78">
-        <f>B14*$B$4%</f>
-        <v>8182.5450145383802</v>
-      </c>
-      <c r="E14" s="15">
-        <f t="shared" si="0"/>
-        <v>5152.4549854616198</v>
-      </c>
-      <c r="F14" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G14" s="78">
-        <f>IFERROR(IF(OR(B14="",D14="",E14=""),0,MAX(0,B14+D14-E14)),"")</f>
-        <v>2482589.1853437372</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="79">
-        <v>5</v>
-      </c>
-      <c r="B15" s="78">
-        <f>B14-E14</f>
-        <v>2474406.6403291989</v>
-      </c>
-      <c r="C15" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D15" s="78">
-        <f>B15*$B$4%</f>
-        <v>8165.5419130863565</v>
-      </c>
-      <c r="E15" s="15">
-        <f t="shared" si="0"/>
-        <v>5169.4580869136435</v>
-      </c>
-      <c r="F15" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G15" s="78">
-        <f>IFERROR(IF(OR(B15="",D15="",E15=""),0,MAX(0,B15+D15-E15)),"")</f>
-        <v>2477402.724155372</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="79">
-        <v>6</v>
-      </c>
-      <c r="B16" s="78">
-        <f>B15-E15</f>
-        <v>2469237.1822422855</v>
-      </c>
-      <c r="C16" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D16" s="78">
-        <f>B16*$B$4%</f>
-        <v>8148.4827013995418</v>
-      </c>
-      <c r="E16" s="15">
-        <f t="shared" si="0"/>
-        <v>5186.5172986004582</v>
-      </c>
-      <c r="F16" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G16" s="78">
-        <f>IFERROR(IF(OR(B16="",D16="",E16=""),0,MAX(0,B16+D16-E16)),"")</f>
-        <v>2472199.1476450842</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="79">
-        <v>7</v>
-      </c>
-      <c r="B17" s="78">
-        <f>B16-E16</f>
-        <v>2464050.6649436848</v>
-      </c>
-      <c r="C17" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D17" s="78">
-        <f>B17*$B$4%</f>
-        <v>8131.3671943141599</v>
-      </c>
-      <c r="E17" s="15">
-        <f t="shared" si="0"/>
-        <v>5203.6328056858401</v>
-      </c>
-      <c r="F17" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G17" s="78">
-        <f>IFERROR(IF(OR(B17="",D17="",E17=""),0,MAX(0,B17+D17-E17)),"")</f>
-        <v>2466978.3993323129</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="79">
-        <v>8</v>
-      </c>
-      <c r="B18" s="78">
-        <f>B17-E17</f>
-        <v>2458847.0321379988</v>
-      </c>
-      <c r="C18" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D18" s="78">
-        <f>B18*$B$4%</f>
-        <v>8114.1952060553958</v>
-      </c>
-      <c r="E18" s="15">
-        <f t="shared" si="0"/>
-        <v>5220.8047939446042</v>
-      </c>
-      <c r="F18" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G18" s="78">
-        <f>IFERROR(IF(OR(B18="",D18="",E18=""),0,MAX(0,B18+D18-E18)),"")</f>
-        <v>2461740.4225501097</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="79">
-        <v>9</v>
-      </c>
-      <c r="B19" s="78">
-        <f>B18-E18</f>
-        <v>2453626.2273440543</v>
-      </c>
-      <c r="C19" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D19" s="78">
-        <f>B19*$B$4%</f>
-        <v>8096.9665502353791</v>
-      </c>
-      <c r="E19" s="15">
-        <f t="shared" si="0"/>
-        <v>5238.0334497646209</v>
-      </c>
-      <c r="F19" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G19" s="78">
-        <f>IFERROR(IF(OR(B19="",D19="",E19=""),0,MAX(0,B19+D19-E19)),"")</f>
-        <v>2456485.1604445246</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="79">
-        <v>10</v>
-      </c>
-      <c r="B20" s="78">
-        <f>B19-E19</f>
-        <v>2448388.1938942894</v>
-      </c>
-      <c r="C20" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D20" s="78">
-        <f>B20*$B$4%</f>
-        <v>8079.6810398511552</v>
-      </c>
-      <c r="E20" s="15">
-        <f t="shared" si="0"/>
-        <v>5255.3189601488448</v>
-      </c>
-      <c r="F20" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G20" s="78">
-        <f>IFERROR(IF(OR(B20="",D20="",E20=""),0,MAX(0,B20+D20-E20)),"")</f>
-        <v>2451212.5559739918</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="79">
-        <v>11</v>
-      </c>
-      <c r="B21" s="78">
-        <f>B20-E20</f>
-        <v>2443132.8749341406</v>
-      </c>
-      <c r="C21" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D21" s="78">
-        <f>B21*$B$4%</f>
-        <v>8062.3384872826637</v>
-      </c>
-      <c r="E21" s="15">
-        <f t="shared" si="0"/>
-        <v>5272.6615127173363</v>
-      </c>
-      <c r="F21" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G21" s="78">
-        <f>IFERROR(IF(OR(B21="",D21="",E21=""),0,MAX(0,B21+D21-E21)),"")</f>
-        <v>2445922.5519087063</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="79">
-        <v>12</v>
-      </c>
-      <c r="B22" s="78">
-        <f>B21-E21</f>
-        <v>2437860.2134214235</v>
-      </c>
-      <c r="C22" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D22" s="78">
-        <f>B22*$B$4%</f>
-        <v>8044.9387042906974</v>
-      </c>
-      <c r="E22" s="15">
-        <f t="shared" si="0"/>
-        <v>5290.0612957093026</v>
-      </c>
-      <c r="F22" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G22" s="78">
-        <f>IFERROR(IF(OR(B22="",D22="",E22=""),0,MAX(0,B22+D22-E22)),"")</f>
-        <v>2440615.0908300052</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="79">
-        <v>13</v>
-      </c>
-      <c r="B23" s="78">
-        <f>B22-E22</f>
-        <v>2432570.1521257143</v>
-      </c>
-      <c r="C23" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D23" s="78">
-        <f>B23*$B$4%</f>
-        <v>8027.4815020148571</v>
-      </c>
-      <c r="E23" s="15">
-        <f t="shared" si="0"/>
-        <v>5307.5184979851429</v>
-      </c>
-      <c r="F23" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G23" s="78">
-        <f>IFERROR(IF(OR(B23="",D23="",E23=""),0,MAX(0,B23+D23-E23)),"")</f>
-        <v>2435290.1151297437</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="79">
-        <v>14</v>
-      </c>
-      <c r="B24" s="15">
-        <f>B23-E23</f>
-        <v>2427262.633627729</v>
-      </c>
-      <c r="C24" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D24" s="78">
-        <f>B24*$B$4%</f>
-        <v>8009.9666909715061</v>
-      </c>
-      <c r="E24" s="15">
-        <f t="shared" si="0"/>
-        <v>5325.0333090284939</v>
-      </c>
-      <c r="F24" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G24" s="15">
-        <f>IFERROR(IF(OR(B24="",D24="",E24=""),0,MAX(0,B24+D24-E24)),"")</f>
-        <v>2429947.5670096721</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="79">
-        <v>15</v>
-      </c>
-      <c r="B25" s="15">
-        <f>B24-E24</f>
-        <v>2421937.6003187005</v>
-      </c>
-      <c r="C25" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D25" s="78">
-        <f>B25*$B$4%</f>
-        <v>7992.3940810517115</v>
-      </c>
-      <c r="E25" s="15">
-        <f t="shared" si="0"/>
-        <v>5342.6059189482885</v>
-      </c>
-      <c r="F25" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G25" s="15">
-        <f>IFERROR(IF(OR(B25="",D25="",E25=""),0,MAX(0,B25+D25-E25)),"")</f>
-        <v>2424587.3884808044</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A26" s="79">
-        <v>16</v>
-      </c>
-      <c r="B26" s="15">
-        <f>B25-E25</f>
-        <v>2416594.9943997525</v>
-      </c>
-      <c r="C26" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D26" s="78">
-        <f>B26*$B$4%</f>
-        <v>7974.7634815191832</v>
-      </c>
-      <c r="E26" s="15">
-        <f t="shared" si="0"/>
-        <v>5360.2365184808168</v>
-      </c>
-      <c r="F26" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G26" s="15">
-        <f>IFERROR(IF(OR(B26="",D26="",E26=""),0,MAX(0,B26+D26-E26)),"")</f>
-        <v>2419209.5213627908</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="79">
-        <v>17</v>
-      </c>
-      <c r="B27" s="15">
-        <f>B26-E26</f>
-        <v>2411234.7578812717</v>
-      </c>
-      <c r="C27" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D27" s="78">
-        <f>B27*$B$4%</f>
-        <v>7957.0747010081968</v>
-      </c>
-      <c r="E27" s="15">
-        <f t="shared" si="0"/>
-        <v>5377.9252989918032</v>
-      </c>
-      <c r="F27" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G27" s="15">
-        <f>IFERROR(IF(OR(B27="",D27="",E27=""),0,MAX(0,B27+D27-E27)),"")</f>
-        <v>2413813.9072832884</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="79">
-        <v>18</v>
-      </c>
-      <c r="B28" s="15">
-        <f>B27-E27</f>
-        <v>2405856.83258228</v>
-      </c>
-      <c r="C28" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D28" s="78">
-        <f>B28*$B$4%</f>
-        <v>7939.3275475215241</v>
-      </c>
-      <c r="E28" s="15">
-        <f t="shared" si="0"/>
-        <v>5395.6724524784759</v>
-      </c>
-      <c r="F28" s="15">
-        <f>$B$7</f>
-        <v>13385</v>
-      </c>
-      <c r="G28" s="15">
-        <f>IFERROR(IF(OR(B28="",D28="",E28=""),0,MAX(0,B28+D28-E28)),"")</f>
-        <v>2408400.4876773227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="79">
-        <v>19</v>
-      </c>
-      <c r="B29" s="15">
-        <f>B28-E28</f>
-        <v>2400461.1601298014</v>
-      </c>
-      <c r="C29" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D29" s="78">
-        <f>B29*$B$4%</f>
-        <v>7921.5218284283446</v>
-      </c>
-      <c r="E29" s="15">
-        <f t="shared" si="0"/>
-        <v>5413.4781715716554</v>
-      </c>
-      <c r="F29" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G29" s="15">
-        <f>IFERROR(IF(OR(B29="",D29="",E29=""),0,MAX(0,B29+D29-E29)),"")</f>
-        <v>2402969.2037866581</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="79">
-        <v>20</v>
-      </c>
-      <c r="B30" s="15">
-        <f>B29-E29</f>
-        <v>2395047.6819582297</v>
-      </c>
-      <c r="C30" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D30" s="78">
-        <f>B30*$B$4%</f>
-        <v>7903.6573504621583</v>
-      </c>
-      <c r="E30" s="15">
-        <f t="shared" si="0"/>
-        <v>5431.3426495378417</v>
-      </c>
-      <c r="F30" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G30" s="15">
-        <f>IFERROR(IF(OR(B30="",D30="",E30=""),0,MAX(0,B30+D30-E30)),"")</f>
-        <v>2397519.9966591536</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="79">
-        <v>21</v>
-      </c>
-      <c r="B31" s="15">
-        <f>B30-E30</f>
-        <v>2389616.3393086917</v>
-      </c>
-      <c r="C31" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D31" s="78">
-        <f>B31*$B$4%</f>
-        <v>7885.733919718682</v>
-      </c>
-      <c r="E31" s="15">
-        <f>F31-C31-D31</f>
-        <v>5449.266080281318</v>
-      </c>
-      <c r="F31" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G31" s="15">
-        <f>IFERROR(IF(OR(B31="",D31="",E31=""),0,MAX(0,B31+D31-E31)),"")</f>
-        <v>2392052.8071481292</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="79">
-        <v>22</v>
-      </c>
-      <c r="B32" s="15">
-        <f>B31-E31</f>
-        <v>2384167.0732284104</v>
-      </c>
-      <c r="C32" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D32" s="78">
-        <f>B32*$B$4%</f>
-        <v>7867.751341653754</v>
-      </c>
-      <c r="E32" s="15">
-        <f t="shared" si="0"/>
-        <v>5467.248658346246</v>
-      </c>
-      <c r="F32" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G32" s="15">
-        <f>IFERROR(IF(OR(B32="",D32="",E32=""),0,MAX(0,B32+D32-E32)),"")</f>
-        <v>2386567.5759117175</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="79">
-        <v>23</v>
-      </c>
-      <c r="B33" s="15">
-        <f>B32-E32</f>
-        <v>2378699.824570064</v>
-      </c>
-      <c r="C33" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D33" s="78">
-        <f>B33*$B$4%</f>
-        <v>7849.7094210812111</v>
-      </c>
-      <c r="E33" s="15">
-        <f t="shared" si="0"/>
-        <v>5485.2905789187889</v>
-      </c>
-      <c r="F33" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
       <c r="G33" s="15">
-        <f>IFERROR(IF(OR(B33="",D33="",E33=""),0,MAX(0,B33+D33-E33)),"")</f>
-        <v>2381064.243412226</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="79">
-        <v>24</v>
-      </c>
-      <c r="B34" s="15">
-        <f>B33-E33</f>
-        <v>2373214.533991145</v>
-      </c>
-      <c r="C34" s="15">
-        <f t="shared" si="2"/>
-        <v>50</v>
-      </c>
-      <c r="D34" s="78">
-        <f>B34*$B$4%</f>
-        <v>7831.6079621707786</v>
-      </c>
-      <c r="E34" s="15">
-        <f t="shared" ref="E34" si="3">F34-C34-D34</f>
-        <v>5503.3920378292214</v>
-      </c>
-      <c r="F34" s="15">
-        <f t="shared" si="1"/>
-        <v>13385</v>
-      </c>
-      <c r="G34" s="15">
-        <f>IFERROR(IF(OR(B34="",D34="",E34=""),0,MAX(0,B34+D34-E34)),"")</f>
+        <f t="shared" si="4"/>
         <v>2375542.7499154862</v>
       </c>
     </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="37" spans="1:7">
-      <c r="A37" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="50" t="s">
+      <c r="A37" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="B38" s="51">
-        <f>SUM(B23:B36)</f>
+      <c r="B37" s="51">
+        <f>SUM(B22:B35)</f>
         <v>28836663.584121786</v>
       </c>
-      <c r="C38" s="51"/>
-      <c r="D38" s="51">
-        <f>SUM(D23:D36)</f>
+      <c r="C37" s="51"/>
+      <c r="D37" s="51">
+        <f>SUM(D22:D35)</f>
         <v>95160.989827601908</v>
       </c>
-      <c r="E38" s="51">
-        <f>SUM(E23:E36)</f>
+      <c r="E37" s="51">
+        <f>SUM(E22:E35)</f>
         <v>64859.010172398099</v>
       </c>
-      <c r="F38" s="51">
-        <f>IFERROR(F36,"")</f>
+      <c r="F37" s="51">
+        <f>IFERROR(F35,"")</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3816,24 +3822,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="65" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="61" t="s">
+      <c r="A2" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
@@ -3863,10 +3869,10 @@
         <v>112</v>
       </c>
       <c r="E4" s="25"/>
-      <c r="F4" s="62" t="s">
+      <c r="F4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="62"/>
+      <c r="G4" s="67"/>
       <c r="H4" s="25"/>
     </row>
     <row r="5" spans="1:8">
@@ -4083,33 +4089,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="22.8">
-      <c r="B2" s="70" t="s">
+      <c r="B2" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="70"/>
-      <c r="D2" s="70"/>
-      <c r="E2" s="70"/>
-      <c r="F2" s="70"/>
+      <c r="C2" s="69"/>
+      <c r="D2" s="69"/>
+      <c r="E2" s="69"/>
+      <c r="F2" s="69"/>
     </row>
     <row r="3" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="4" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B4" s="71" t="s">
+      <c r="B4" s="70" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
+      <c r="C4" s="70"/>
+      <c r="D4" s="70"/>
+      <c r="E4" s="70"/>
+      <c r="F4" s="70"/>
     </row>
     <row r="5" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="6" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B6" s="67" t="s">
+      <c r="B6" s="71" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="67"/>
-      <c r="D6" s="67"/>
-      <c r="E6" s="67"/>
-      <c r="F6" s="67"/>
+      <c r="C6" s="71"/>
+      <c r="D6" s="71"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="71"/>
     </row>
     <row r="7" spans="2:6" ht="21.75" customHeight="1">
       <c r="B7" s="16" t="s">
@@ -4141,34 +4147,34 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="16.8">
-      <c r="B9" s="68" t="s">
+      <c r="B9" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="68"/>
-      <c r="E9" s="69">
+      <c r="C9" s="72"/>
+      <c r="E9" s="73">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(F8),C8&gt;0,F8&gt;0),SQRT(C8^2+F8^2),"Fyll inn a og b")</f>
         <v>5</v>
       </c>
-      <c r="F9" s="69"/>
+      <c r="F9" s="73"/>
     </row>
     <row r="10" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B10" s="63" t="s">
+      <c r="B10" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
-      <c r="E10" s="63"/>
-      <c r="F10" s="63"/>
+      <c r="C10" s="68"/>
+      <c r="D10" s="68"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="68"/>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="12" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
     </row>
     <row r="13" spans="2:6" ht="9.75" customHeight="1">
       <c r="B13" s="16" t="s">
@@ -4200,34 +4206,34 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="16.8">
-      <c r="B15" s="68" t="s">
+      <c r="B15" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="68"/>
-      <c r="E15" s="69">
+      <c r="C15" s="72"/>
+      <c r="E15" s="73">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(F14),C14&gt;0,F14&gt;0,C14&gt;F14),SQRT(C14^2-F14^2),IF(C14&lt;=F14,"c må være større enn b","Fyll inn c og b"))</f>
         <v>3</v>
       </c>
-      <c r="F15" s="69"/>
+      <c r="F15" s="73"/>
     </row>
     <row r="16" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B16" s="63" t="s">
+      <c r="B16" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="63"/>
-      <c r="D16" s="63"/>
-      <c r="E16" s="63"/>
-      <c r="F16" s="63"/>
+      <c r="C16" s="68"/>
+      <c r="D16" s="68"/>
+      <c r="E16" s="68"/>
+      <c r="F16" s="68"/>
     </row>
     <row r="17" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="18" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B18" s="67" t="s">
+      <c r="B18" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="71"/>
+      <c r="F18" s="71"/>
     </row>
     <row r="19" spans="2:6" ht="21.75" customHeight="1">
       <c r="B19" s="16" t="s">
@@ -4259,44 +4265,44 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="16.8">
-      <c r="B21" s="68" t="s">
+      <c r="B21" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="68"/>
-      <c r="E21" s="69">
+      <c r="C21" s="72"/>
+      <c r="E21" s="73">
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(F20),C20&gt;0,F20&gt;0,C20&gt;F20),SQRT(C20^2-F20^2),IF(C20&lt;=F20,"c må være større enn a","Fyll inn c og a"))</f>
         <v>4</v>
       </c>
-      <c r="F21" s="69"/>
+      <c r="F21" s="73"/>
     </row>
     <row r="22" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B22" s="63" t="s">
+      <c r="B22" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="63"/>
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
     </row>
     <row r="23" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="24" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B24" s="64" t="s">
+      <c r="B24" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="64"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="64"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="74"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
     </row>
     <row r="25" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B25" s="65" t="s">
+      <c r="B25" s="75" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="65"/>
-      <c r="E25" s="66" t="s">
+      <c r="C25" s="75"/>
+      <c r="E25" s="76" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="66"/>
+      <c r="F25" s="76"/>
     </row>
     <row r="26" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="27" spans="2:6" ht="21.75" customHeight="1"/>
@@ -4314,12 +4320,6 @@
     <row r="39" ht="21.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:C25"/>
@@ -4331,6 +4331,12 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4350,20 +4356,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="83"/>
+      <c r="B1" s="62"/>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="84"/>
-      <c r="B2" s="84"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="63"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="59" t="s">
+      <c r="B3" s="57" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4384,16 +4390,16 @@
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="B6" s="82"/>
+      <c r="B6" s="61"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="B7" s="57">
+      <c r="B7" s="56">
         <f>B4*(1+B5/100)</f>
         <v>1250</v>
       </c>
@@ -4402,26 +4408,26 @@
       <c r="A8" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="57">
+      <c r="B8" s="56">
         <f>B7-B4</f>
         <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.8" customHeight="1">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="62" t="s">
         <v>123</v>
       </c>
-      <c r="B11" s="83"/>
+      <c r="B11" s="62"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="84"/>
-      <c r="B12" s="84"/>
+      <c r="A12" s="63"/>
+      <c r="B12" s="63"/>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="52" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="57" t="s">
         <v>117</v>
       </c>
     </row>
@@ -4442,16 +4448,16 @@
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="82" t="s">
+      <c r="A16" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="B16" s="82"/>
+      <c r="B16" s="61"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="B17" s="57">
+      <c r="B17" s="56">
         <f>IF(1+B15/100=0,"Ugyldig: 0%",B14/(1+B15/100))</f>
         <v>1000</v>
       </c>
@@ -4460,20 +4466,20 @@
       <c r="A18" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="B18" s="57">
+      <c r="B18" s="56">
         <f>IF(ISNUMBER(B17),B14-B17,"")</f>
         <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.8" customHeight="1">
-      <c r="A21" s="83" t="s">
+      <c r="A21" s="62" t="s">
         <v>126</v>
       </c>
-      <c r="B21" s="83"/>
+      <c r="B21" s="62"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="84"/>
-      <c r="B22" s="84"/>
+      <c r="A22" s="63"/>
+      <c r="B22" s="63"/>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="52" t="s">
@@ -4488,7 +4494,7 @@
         <v>118</v>
       </c>
       <c r="B24" s="55">
-        <v>1000</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -4496,40 +4502,40 @@
         <v>127</v>
       </c>
       <c r="B25" s="55">
-        <v>1250</v>
+        <v>50</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="82" t="s">
+      <c r="A26" s="61" t="s">
         <v>120</v>
       </c>
-      <c r="B26" s="82"/>
+      <c r="B26" s="61"/>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="54" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="56">
-        <f>IF(B24=0,"Ugyldig: startverdi er 0",(B25-B24)/B24*100)</f>
-        <v>25</v>
+      <c r="B27" s="83">
+        <f>IF(B24=0,"Ugyldig: startverdi er 0",(B25-B24)/B24*100)/100</f>
+        <v>1.5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="54" t="s">
         <v>122</v>
       </c>
-      <c r="B28" s="57">
+      <c r="B28" s="84">
         <f>B25-B24</f>
-        <v>250</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="54" t="s">
         <v>129</v>
       </c>
-      <c r="B29" s="58" t="str">
+      <c r="B29" s="85" t="str">
         <f>IF(ISNUMBER(B27),TEXT(B27,"0.00")&amp;" %",B27)</f>
-        <v>25.00 %</v>
+        <v>1.50 %</v>
       </c>
     </row>
   </sheetData>
@@ -4554,20 +4560,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="78" t="s">
         <v>132</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
-      <c r="D1" s="73"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A3" s="72" t="s">
+      <c r="A3" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="72"/>
-      <c r="C3" s="72"/>
-      <c r="D3" s="72"/>
+      <c r="B3" s="77"/>
+      <c r="C3" s="77"/>
+      <c r="D3" s="77"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="21" t="s">
@@ -4648,12 +4654,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A11" s="72" t="s">
+      <c r="A11" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
+      <c r="B11" s="77"/>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="21" t="s">
@@ -4734,12 +4740,12 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A19" s="72" t="s">
+      <c r="A19" s="77" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
+      <c r="B19" s="77"/>
+      <c r="C19" s="77"/>
+      <c r="D19" s="77"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="21" t="s">
@@ -4821,12 +4827,12 @@
     </row>
     <row r="27" spans="1:4" ht="19.5" customHeight="1"/>
     <row r="28" spans="1:4" ht="15.6">
-      <c r="A28" s="72" t="s">
+      <c r="A28" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="72"/>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
+      <c r="B28" s="77"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="77"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="21" t="s">
@@ -4855,12 +4861,12 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.6">
-      <c r="A32" s="72" t="s">
+      <c r="A32" s="77" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="72"/>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
+      <c r="B32" s="77"/>
+      <c r="C32" s="77"/>
+      <c r="D32" s="77"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="21" t="s">
@@ -4939,30 +4945,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
+      <c r="A1" s="79" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="75" t="s">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="75"/>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+      <c r="I2" s="80"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4973,10 +4979,10 @@
         <f>AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;"")</f>
         <v>0</v>
       </c>
-      <c r="K3" s="76" t="s">
+      <c r="K3" s="81" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="76"/>
+      <c r="L3" s="81"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
       <c r="K4" s="4" t="s">
@@ -5076,11 +5082,11 @@
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),(IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),SUM(C8:C27),1)+1)/2,0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="77" t="str">
+      <c r="K8" s="82" t="str">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),"✅ Klar – se Histogram-fanen","⚠️ Fyll inn data i kolonne A og C")</f>
         <v>⚠️ Fyll inn data i kolonne A og C</v>
       </c>
-      <c r="L8" s="77"/>
+      <c r="L8" s="82"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
       <c r="A9" s="2"/>

--- a/SnorresMatteskjema.xlsx
+++ b/SnorresMatteskjema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97B4C362-27B2-4773-BD5D-F08FA95CF84A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3767B6D5-7F90-47EC-BC1D-A417D28D808E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="501" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="501" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Utregning" sheetId="2" state="hidden" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="143">
   <si>
     <t>📊 Histogram – Sentralmål i gruppert materiale</t>
   </si>
@@ -364,12 +364,6 @@
     <t>Histogram</t>
   </si>
   <si>
-    <t xml:space="preserve">Nedbetaling av lån </t>
-  </si>
-  <si>
-    <t>Mattetype</t>
-  </si>
-  <si>
     <t>1P</t>
   </si>
   <si>
@@ -388,9 +382,6 @@
     <t>frekvens · observasjon</t>
   </si>
   <si>
-    <t>Snarveier</t>
-  </si>
-  <si>
     <t>📈 FINN NY VERDI</t>
   </si>
   <si>
@@ -439,20 +430,6 @@
     <t>Prosentregning</t>
   </si>
   <si>
-    <r>
-      <t>Lykke til med eksamen! Hilsen Snorre Saus</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <color rgb="FF2EC4A1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>❤</t>
-    </r>
-  </si>
-  <si>
     <t>ENHETOMGJØRING</t>
   </si>
   <si>
@@ -472,6 +449,30 @@
   </si>
   <si>
     <t>Lånnedbetaling</t>
+  </si>
+  <si>
+    <t>🏦</t>
+  </si>
+  <si>
+    <t>📊</t>
+  </si>
+  <si>
+    <t>📐</t>
+  </si>
+  <si>
+    <t>Nedbetaling av lån</t>
+  </si>
+  <si>
+    <t>💯</t>
+  </si>
+  <si>
+    <t>📏</t>
+  </si>
+  <si>
+    <t>📈</t>
+  </si>
+  <si>
+    <t>Snorres Matteskjema</t>
   </si>
 </sst>
 </file>
@@ -482,7 +483,7 @@
     <numFmt numFmtId="164" formatCode="0.0#"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -697,41 +698,9 @@
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="25"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="25"/>
-      <color rgb="FF2EC4A1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="25"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <i/>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FF2EC4A1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -749,8 +718,52 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="28"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="42">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -891,12 +904,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1FBB96"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF2E3047"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -911,12 +918,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF2E3047"/>
         <bgColor rgb="FF1F3864"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF373A4B"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -965,6 +966,41 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFCCFFCC"/>
         <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1A2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E86AB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA23B72"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF18F01"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC73E1D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3B1F2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44BBA4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1041,7 +1077,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1148,26 +1184,19 @@
     <xf numFmtId="165" fontId="7" fillId="9" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="28" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="28" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="34" fillId="25" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="35" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="32" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="15" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="25" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="34" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1176,10 +1205,10 @@
     <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="30" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="15" fillId="28" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1188,14 +1217,14 @@
     <xf numFmtId="1" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="29" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1237,7 +1266,7 @@
     <xf numFmtId="0" fontId="24" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1255,15 +1284,84 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="1" fillId="35" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="1" fillId="33" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="15" fillId="36" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="15" fillId="34" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="36" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="36" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="36" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="37" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="37" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="39" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="39" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="41" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2869,85 +2967,384 @@
   <sheetPr>
     <tabColor rgb="FF2EC4A1"/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="60" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="41" customWidth="1"/>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="14" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="31.8">
-      <c r="A1" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B1" s="43" t="s">
+    <row r="1" spans="1:13" ht="23.4">
+      <c r="A1" s="79" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="79"/>
+      <c r="C1" s="79"/>
+      <c r="D1" s="79"/>
+      <c r="E1" s="79"/>
+      <c r="F1" s="79"/>
+      <c r="G1" s="79"/>
+      <c r="H1" s="79"/>
+      <c r="I1" s="79"/>
+      <c r="J1" s="79"/>
+      <c r="K1" s="79"/>
+      <c r="L1" s="79"/>
+      <c r="M1" s="79"/>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="B3" s="80" t="s">
+        <v>135</v>
+      </c>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="82" t="s">
+        <v>136</v>
+      </c>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="J3" s="84" t="s">
+        <v>137</v>
+      </c>
+      <c r="K3" s="85"/>
+      <c r="L3" s="85"/>
+      <c r="M3" s="85"/>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="85"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="85"/>
+      <c r="M4" s="85"/>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="J5" s="85"/>
+      <c r="K5" s="85"/>
+      <c r="L5" s="85"/>
+      <c r="M5" s="85"/>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="83"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="83"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="85"/>
+      <c r="L6" s="85"/>
+      <c r="M6" s="85"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="B7" s="98" t="s">
+        <v>138</v>
+      </c>
+      <c r="C7" s="99"/>
+      <c r="D7" s="99"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="100" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="108" t="s">
+        <v>103</v>
+      </c>
+      <c r="K7" s="109"/>
+      <c r="L7" s="109"/>
+      <c r="M7" s="109"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="B8" s="99"/>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="99"/>
+      <c r="F8" s="101"/>
+      <c r="G8" s="101"/>
+      <c r="H8" s="101"/>
+      <c r="I8" s="101"/>
+      <c r="J8" s="109"/>
+      <c r="K8" s="109"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="109"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="B9" s="99"/>
+      <c r="C9" s="99"/>
+      <c r="D9" s="99"/>
+      <c r="E9" s="99"/>
+      <c r="F9" s="101"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="109"/>
+      <c r="K9" s="109"/>
+      <c r="L9" s="109"/>
+      <c r="M9" s="109"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="B10" s="86" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="31.2">
-      <c r="A2" s="44" t="s">
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="83"/>
+      <c r="H10" s="83"/>
+      <c r="I10" s="83"/>
+      <c r="J10" s="88" t="s">
         <v>106</v>
       </c>
-      <c r="B2" s="45" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="31.2">
-      <c r="A3" s="46" t="s">
-        <v>102</v>
-      </c>
-      <c r="B3" s="47" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="31.2">
-      <c r="A4" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="45" t="s">
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="83"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="B16" s="89" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="90"/>
+      <c r="D16" s="90"/>
+      <c r="E16" s="90"/>
+      <c r="F16" s="91" t="s">
+        <v>140</v>
+      </c>
+      <c r="G16" s="92"/>
+      <c r="H16" s="92"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="93" t="s">
+        <v>141</v>
+      </c>
+      <c r="K16" s="94"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="94"/>
+    </row>
+    <row r="17" spans="2:13">
+      <c r="B17" s="90"/>
+      <c r="C17" s="90"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="92"/>
+      <c r="G17" s="92"/>
+      <c r="H17" s="92"/>
+      <c r="I17" s="92"/>
+      <c r="J17" s="94"/>
+      <c r="K17" s="94"/>
+      <c r="L17" s="94"/>
+      <c r="M17" s="94"/>
+    </row>
+    <row r="18" spans="2:13">
+      <c r="B18" s="90"/>
+      <c r="C18" s="90"/>
+      <c r="D18" s="90"/>
+      <c r="E18" s="90"/>
+      <c r="F18" s="92"/>
+      <c r="G18" s="92"/>
+      <c r="H18" s="92"/>
+      <c r="I18" s="92"/>
+      <c r="J18" s="94"/>
+      <c r="K18" s="94"/>
+      <c r="L18" s="94"/>
+      <c r="M18" s="94"/>
+    </row>
+    <row r="19" spans="2:13">
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="92"/>
+      <c r="G19" s="92"/>
+      <c r="H19" s="92"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="94"/>
+      <c r="K19" s="94"/>
+      <c r="L19" s="94"/>
+      <c r="M19" s="94"/>
+    </row>
+    <row r="20" spans="2:13">
+      <c r="B20" s="102" t="s">
+        <v>127</v>
+      </c>
+      <c r="C20" s="103"/>
+      <c r="D20" s="103"/>
+      <c r="E20" s="103"/>
+      <c r="F20" s="104" t="s">
+        <v>104</v>
+      </c>
+      <c r="G20" s="105"/>
+      <c r="H20" s="105"/>
+      <c r="I20" s="105"/>
+      <c r="J20" s="106" t="s">
+        <v>105</v>
+      </c>
+      <c r="K20" s="107"/>
+      <c r="L20" s="107"/>
+      <c r="M20" s="107"/>
+    </row>
+    <row r="21" spans="2:13">
+      <c r="B21" s="103"/>
+      <c r="C21" s="103"/>
+      <c r="D21" s="103"/>
+      <c r="E21" s="103"/>
+      <c r="F21" s="105"/>
+      <c r="G21" s="105"/>
+      <c r="H21" s="105"/>
+      <c r="I21" s="105"/>
+      <c r="J21" s="107"/>
+      <c r="K21" s="107"/>
+      <c r="L21" s="107"/>
+      <c r="M21" s="107"/>
+    </row>
+    <row r="22" spans="2:13">
+      <c r="B22" s="103"/>
+      <c r="C22" s="103"/>
+      <c r="D22" s="103"/>
+      <c r="E22" s="103"/>
+      <c r="F22" s="105"/>
+      <c r="G22" s="105"/>
+      <c r="H22" s="105"/>
+      <c r="I22" s="105"/>
+      <c r="J22" s="107"/>
+      <c r="K22" s="107"/>
+      <c r="L22" s="107"/>
+      <c r="M22" s="107"/>
+    </row>
+    <row r="23" spans="2:13">
+      <c r="B23" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="C23" s="90"/>
+      <c r="D23" s="90"/>
+      <c r="E23" s="90"/>
+      <c r="F23" s="96" t="s">
+        <v>106</v>
+      </c>
+      <c r="G23" s="92"/>
+      <c r="H23" s="92"/>
+      <c r="I23" s="92"/>
+      <c r="J23" s="97" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="31.2">
-      <c r="A5" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" s="47" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="31.2">
-      <c r="A6" s="44" t="s">
-        <v>104</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="31.2">
-      <c r="A7" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="49" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="18.600000000000001">
-      <c r="A11" s="48" t="s">
-        <v>131</v>
-      </c>
+      <c r="K23" s="94"/>
+      <c r="L23" s="94"/>
+      <c r="M23" s="94"/>
+    </row>
+    <row r="24" spans="2:13">
+      <c r="B24" s="90"/>
+      <c r="C24" s="90"/>
+      <c r="D24" s="90"/>
+      <c r="E24" s="90"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="92"/>
+      <c r="I24" s="92"/>
+      <c r="J24" s="94"/>
+      <c r="K24" s="94"/>
+      <c r="L24" s="94"/>
+      <c r="M24" s="94"/>
+    </row>
+    <row r="25" spans="2:13">
+      <c r="B25" s="90"/>
+      <c r="C25" s="90"/>
+      <c r="D25" s="90"/>
+      <c r="E25" s="90"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="92"/>
+      <c r="I25" s="92"/>
+      <c r="J25" s="94"/>
+      <c r="K25" s="94"/>
+      <c r="L25" s="94"/>
+      <c r="M25" s="94"/>
     </row>
   </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="B20:E22"/>
+    <mergeCell ref="F20:I22"/>
+    <mergeCell ref="J20:M22"/>
+    <mergeCell ref="B23:E25"/>
+    <mergeCell ref="F23:I25"/>
+    <mergeCell ref="J23:M25"/>
+    <mergeCell ref="B10:E12"/>
+    <mergeCell ref="F10:I12"/>
+    <mergeCell ref="J10:M12"/>
+    <mergeCell ref="B16:E19"/>
+    <mergeCell ref="F16:I19"/>
+    <mergeCell ref="J16:M19"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B3:E6"/>
+    <mergeCell ref="F3:I6"/>
+    <mergeCell ref="J3:M6"/>
+    <mergeCell ref="B7:E9"/>
+    <mergeCell ref="F7:I9"/>
+    <mergeCell ref="J7:M9"/>
+  </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A2" location="'Nedbetaling av lån'!A1" display="Nedbetaling av lån" xr:uid="{0CB09D8D-9E88-4852-8FD4-B9765CE7E1C1}"/>
-    <hyperlink ref="A3" location="Frekvenstabell!A1" display="Frekvenstabell" xr:uid="{28E08C63-88A6-4D97-9B1A-F5FF0A420FB3}"/>
-    <hyperlink ref="A4" location="'Pytagoras-kalkulator'!A1" display="Pytagoras-kalkulator" xr:uid="{BEADACE7-246C-4EF6-8634-3AA71ED8FA4F}"/>
-    <hyperlink ref="A6" location="'Omgjøring av enheter'!A1" display="Omgjøring av enheter" xr:uid="{828AF539-531C-4E0F-AE61-68AF698F14FB}"/>
-    <hyperlink ref="A7" location="'Inndata til histogram'!A1" display="Histogram" xr:uid="{75770D72-E7A2-42D1-AF93-D95468F62E44}"/>
-    <hyperlink ref="A5" location="Prosentregning!A1" display="Prosentregning" xr:uid="{F5EF3D7C-BAB0-4C2C-893B-C7F83BD63E4A}"/>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{9100B2D1-BB5C-473B-8117-69FF6BC0C34C}"/>
+    <hyperlink ref="F7" r:id="rId2" xr:uid="{25B6C355-FE5F-4BC8-9B5D-AD210EACF735}"/>
+    <hyperlink ref="J7" r:id="rId3" xr:uid="{78D6EB08-BDC3-44B9-81B4-3E4F9C15DF16}"/>
+    <hyperlink ref="B20" r:id="rId4" xr:uid="{5948A52C-BBE9-4001-AB82-9F34F0AEA6A9}"/>
+    <hyperlink ref="F20" r:id="rId5" xr:uid="{2BFCF540-747D-43C1-A84D-355FE742C9B8}"/>
+    <hyperlink ref="J20" r:id="rId6" xr:uid="{1AE6CA7B-1A22-4890-A1A2-B1897DDAD336}"/>
+    <hyperlink ref="B7:E9" location="'Nedbetaling av lån'!A1" display="Nedbetaling av lån" xr:uid="{F135D8D2-170F-45B5-917D-007F94E54D52}"/>
+    <hyperlink ref="F7:I9" location="Frekvenstabell!A1" display="Frekvenstabell" xr:uid="{279ABC88-D135-4D6C-A3F8-653BF5A6D963}"/>
+    <hyperlink ref="J7:M9" location="'Pytagoras-kalkulator'!A1" display="Pytagoras-kalkulator" xr:uid="{987E3396-59D4-4067-8A03-3263C550FE70}"/>
+    <hyperlink ref="B20:E22" location="Prosentregning!A1" display="Prosentregning" xr:uid="{F8220CE7-CA4C-4655-AA73-1517D65F898F}"/>
+    <hyperlink ref="F20:I22" location="'Omgjøring av enheter'!A1" display="Omgjøring av enheter" xr:uid="{305A8267-9C4C-4A83-84BC-53894247AC72}"/>
+    <hyperlink ref="J20:M22" location="'Inndata til histogram'!A1" display="Histogram" xr:uid="{5EC64D6B-1C60-41C1-9CB8-8513D0D2E5A4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId7"/>
 </worksheet>
 </file>
 
@@ -2969,13 +3366,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.2" customHeight="1">
-      <c r="A1" s="64" t="s">
-        <v>138</v>
-      </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
+      <c r="A1" s="57" t="s">
+        <v>134</v>
+      </c>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -2987,7 +3384,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="9" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B3" s="11">
         <v>0.33</v>
@@ -2995,15 +3392,15 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="9" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B4" s="12">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="21" customHeight="1">
-      <c r="A5" s="60" t="s">
-        <v>133</v>
+      <c r="A5" s="53" t="s">
+        <v>129</v>
       </c>
       <c r="B5" s="12">
         <v>50</v>
@@ -3011,7 +3408,7 @@
     </row>
     <row r="6" spans="1:7" ht="15.6" customHeight="1">
       <c r="A6" s="13" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B6" s="12">
         <v>13385</v>
@@ -3026,7 +3423,7 @@
         <v>24</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="D8" s="42" t="s">
         <v>25</v>
@@ -3035,17 +3432,17 @@
         <v>26</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G8" s="42" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="59">
-        <v>0</v>
-      </c>
-      <c r="B9" s="58">
+      <c r="A9" s="52">
+        <v>0</v>
+      </c>
+      <c r="B9" s="51">
         <f>B2</f>
         <v>2500000</v>
       </c>
@@ -3065,16 +3462,16 @@
         <f>$B$6</f>
         <v>13385</v>
       </c>
-      <c r="G9" s="58">
+      <c r="G9" s="51">
         <f>D9+E9</f>
         <v>13335</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="59">
+      <c r="A10" s="52">
         <v>1</v>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="51">
         <f t="shared" ref="B10:B33" si="0">B9-E9</f>
         <v>2494915</v>
       </c>
@@ -3082,7 +3479,7 @@
         <f>$B$5</f>
         <v>50</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="51">
         <f t="shared" ref="D10:D33" si="1">B10*$B$3%</f>
         <v>8233.2194999999992</v>
       </c>
@@ -3094,16 +3491,16 @@
         <f t="shared" ref="F10:F33" si="3">$B$6</f>
         <v>13385</v>
       </c>
-      <c r="G10" s="58">
+      <c r="G10" s="51">
         <f t="shared" ref="G10:G33" si="4">IFERROR(IF(OR(B10="",D10="",E10=""),0,MAX(0,B10+D10-E10)),"")</f>
         <v>2498046.4390000002</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="59">
+      <c r="A11" s="52">
         <v>2</v>
       </c>
-      <c r="B11" s="58">
+      <c r="B11" s="51">
         <f t="shared" si="0"/>
         <v>2489813.2195000001</v>
       </c>
@@ -3111,7 +3508,7 @@
         <f t="shared" ref="C11:C33" si="5">$B$5</f>
         <v>50</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="51">
         <f t="shared" si="1"/>
         <v>8216.3836243500009</v>
       </c>
@@ -3123,16 +3520,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G11" s="58">
+      <c r="G11" s="51">
         <f t="shared" si="4"/>
         <v>2492910.9867487005</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="59">
+      <c r="A12" s="52">
         <v>3</v>
       </c>
-      <c r="B12" s="58">
+      <c r="B12" s="51">
         <f t="shared" si="0"/>
         <v>2484694.6031243503</v>
       </c>
@@ -3140,7 +3537,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="51">
         <f t="shared" si="1"/>
         <v>8199.4921903103568</v>
       </c>
@@ -3152,16 +3549,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G12" s="58">
+      <c r="G12" s="51">
         <f t="shared" si="4"/>
         <v>2487758.5875049708</v>
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="59">
+      <c r="A13" s="52">
         <v>4</v>
       </c>
-      <c r="B13" s="58">
+      <c r="B13" s="51">
         <f t="shared" si="0"/>
         <v>2479559.0953146606</v>
       </c>
@@ -3169,7 +3566,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="51">
         <f t="shared" si="1"/>
         <v>8182.5450145383802</v>
       </c>
@@ -3181,16 +3578,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G13" s="58">
+      <c r="G13" s="51">
         <f t="shared" si="4"/>
         <v>2482589.1853437372</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="59">
+      <c r="A14" s="52">
         <v>5</v>
       </c>
-      <c r="B14" s="58">
+      <c r="B14" s="51">
         <f t="shared" si="0"/>
         <v>2474406.6403291989</v>
       </c>
@@ -3198,7 +3595,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D14" s="58">
+      <c r="D14" s="51">
         <f t="shared" si="1"/>
         <v>8165.5419130863565</v>
       </c>
@@ -3210,16 +3607,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G14" s="58">
+      <c r="G14" s="51">
         <f t="shared" si="4"/>
         <v>2477402.724155372</v>
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="59">
+      <c r="A15" s="52">
         <v>6</v>
       </c>
-      <c r="B15" s="58">
+      <c r="B15" s="51">
         <f t="shared" si="0"/>
         <v>2469237.1822422855</v>
       </c>
@@ -3227,7 +3624,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="51">
         <f t="shared" si="1"/>
         <v>8148.4827013995418</v>
       </c>
@@ -3239,16 +3636,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G15" s="51">
         <f t="shared" si="4"/>
         <v>2472199.1476450842</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="59">
+      <c r="A16" s="52">
         <v>7</v>
       </c>
-      <c r="B16" s="58">
+      <c r="B16" s="51">
         <f t="shared" si="0"/>
         <v>2464050.6649436848</v>
       </c>
@@ -3256,7 +3653,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="51">
         <f t="shared" si="1"/>
         <v>8131.3671943141599</v>
       </c>
@@ -3268,16 +3665,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G16" s="51">
         <f t="shared" si="4"/>
         <v>2466978.3993323129</v>
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="59">
+      <c r="A17" s="52">
         <v>8</v>
       </c>
-      <c r="B17" s="58">
+      <c r="B17" s="51">
         <f t="shared" si="0"/>
         <v>2458847.0321379988</v>
       </c>
@@ -3285,7 +3682,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="51">
         <f t="shared" si="1"/>
         <v>8114.1952060553958</v>
       </c>
@@ -3297,16 +3694,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G17" s="51">
         <f t="shared" si="4"/>
         <v>2461740.4225501097</v>
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="59">
+      <c r="A18" s="52">
         <v>9</v>
       </c>
-      <c r="B18" s="58">
+      <c r="B18" s="51">
         <f t="shared" si="0"/>
         <v>2453626.2273440543</v>
       </c>
@@ -3314,7 +3711,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="51">
         <f t="shared" si="1"/>
         <v>8096.9665502353791</v>
       </c>
@@ -3326,16 +3723,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="51">
         <f t="shared" si="4"/>
         <v>2456485.1604445246</v>
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="59">
+      <c r="A19" s="52">
         <v>10</v>
       </c>
-      <c r="B19" s="58">
+      <c r="B19" s="51">
         <f t="shared" si="0"/>
         <v>2448388.1938942894</v>
       </c>
@@ -3343,7 +3740,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="51">
         <f t="shared" si="1"/>
         <v>8079.6810398511552</v>
       </c>
@@ -3355,16 +3752,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G19" s="58">
+      <c r="G19" s="51">
         <f t="shared" si="4"/>
         <v>2451212.5559739918</v>
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="59">
+      <c r="A20" s="52">
         <v>11</v>
       </c>
-      <c r="B20" s="58">
+      <c r="B20" s="51">
         <f t="shared" si="0"/>
         <v>2443132.8749341406</v>
       </c>
@@ -3372,7 +3769,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="51">
         <f t="shared" si="1"/>
         <v>8062.3384872826637</v>
       </c>
@@ -3384,16 +3781,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G20" s="58">
+      <c r="G20" s="51">
         <f t="shared" si="4"/>
         <v>2445922.5519087063</v>
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="59">
+      <c r="A21" s="52">
         <v>12</v>
       </c>
-      <c r="B21" s="58">
+      <c r="B21" s="51">
         <f t="shared" si="0"/>
         <v>2437860.2134214235</v>
       </c>
@@ -3401,7 +3798,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D21" s="58">
+      <c r="D21" s="51">
         <f t="shared" si="1"/>
         <v>8044.9387042906974</v>
       </c>
@@ -3413,16 +3810,16 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G21" s="58">
+      <c r="G21" s="51">
         <f t="shared" si="4"/>
         <v>2440615.0908300052</v>
       </c>
     </row>
     <row r="22" spans="1:7">
-      <c r="A22" s="59">
+      <c r="A22" s="52">
         <v>13</v>
       </c>
-      <c r="B22" s="58">
+      <c r="B22" s="51">
         <f t="shared" si="0"/>
         <v>2432570.1521257143</v>
       </c>
@@ -3430,7 +3827,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D22" s="58">
+      <c r="D22" s="51">
         <f t="shared" si="1"/>
         <v>8027.4815020148571</v>
       </c>
@@ -3442,13 +3839,13 @@
         <f t="shared" si="3"/>
         <v>13385</v>
       </c>
-      <c r="G22" s="58">
+      <c r="G22" s="51">
         <f t="shared" si="4"/>
         <v>2435290.1151297437</v>
       </c>
     </row>
     <row r="23" spans="1:7">
-      <c r="A23" s="59">
+      <c r="A23" s="52">
         <v>14</v>
       </c>
       <c r="B23" s="15">
@@ -3459,7 +3856,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D23" s="58">
+      <c r="D23" s="51">
         <f t="shared" si="1"/>
         <v>8009.9666909715061</v>
       </c>
@@ -3477,7 +3874,7 @@
       </c>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="59">
+      <c r="A24" s="52">
         <v>15</v>
       </c>
       <c r="B24" s="15">
@@ -3488,7 +3885,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D24" s="58">
+      <c r="D24" s="51">
         <f t="shared" si="1"/>
         <v>7992.3940810517115</v>
       </c>
@@ -3506,7 +3903,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" ht="19.5" customHeight="1">
-      <c r="A25" s="59">
+      <c r="A25" s="52">
         <v>16</v>
       </c>
       <c r="B25" s="15">
@@ -3517,7 +3914,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="51">
         <f t="shared" si="1"/>
         <v>7974.7634815191832</v>
       </c>
@@ -3535,7 +3932,7 @@
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" s="59">
+      <c r="A26" s="52">
         <v>17</v>
       </c>
       <c r="B26" s="15">
@@ -3546,7 +3943,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D26" s="58">
+      <c r="D26" s="51">
         <f t="shared" si="1"/>
         <v>7957.0747010081968</v>
       </c>
@@ -3564,7 +3961,7 @@
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" s="59">
+      <c r="A27" s="52">
         <v>18</v>
       </c>
       <c r="B27" s="15">
@@ -3575,7 +3972,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D27" s="58">
+      <c r="D27" s="51">
         <f t="shared" si="1"/>
         <v>7939.3275475215241</v>
       </c>
@@ -3593,7 +3990,7 @@
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" s="59">
+      <c r="A28" s="52">
         <v>19</v>
       </c>
       <c r="B28" s="15">
@@ -3604,7 +4001,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D28" s="58">
+      <c r="D28" s="51">
         <f t="shared" si="1"/>
         <v>7921.5218284283446</v>
       </c>
@@ -3622,7 +4019,7 @@
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" s="59">
+      <c r="A29" s="52">
         <v>20</v>
       </c>
       <c r="B29" s="15">
@@ -3633,7 +4030,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D29" s="58">
+      <c r="D29" s="51">
         <f t="shared" si="1"/>
         <v>7903.6573504621583</v>
       </c>
@@ -3651,7 +4048,7 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="59">
+      <c r="A30" s="52">
         <v>21</v>
       </c>
       <c r="B30" s="15">
@@ -3662,7 +4059,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D30" s="58">
+      <c r="D30" s="51">
         <f t="shared" si="1"/>
         <v>7885.733919718682</v>
       </c>
@@ -3680,7 +4077,7 @@
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" s="59">
+      <c r="A31" s="52">
         <v>22</v>
       </c>
       <c r="B31" s="15">
@@ -3691,7 +4088,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D31" s="58">
+      <c r="D31" s="51">
         <f t="shared" si="1"/>
         <v>7867.751341653754</v>
       </c>
@@ -3709,7 +4106,7 @@
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" s="59">
+      <c r="A32" s="52">
         <v>23</v>
       </c>
       <c r="B32" s="15">
@@ -3720,7 +4117,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D32" s="58">
+      <c r="D32" s="51">
         <f t="shared" si="1"/>
         <v>7849.7094210812111</v>
       </c>
@@ -3738,7 +4135,7 @@
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" s="59">
+      <c r="A33" s="52">
         <v>24</v>
       </c>
       <c r="B33" s="15">
@@ -3749,7 +4146,7 @@
         <f t="shared" si="5"/>
         <v>50</v>
       </c>
-      <c r="D33" s="58">
+      <c r="D33" s="51">
         <f t="shared" si="1"/>
         <v>7831.6079621707786</v>
       </c>
@@ -3772,23 +4169,23 @@
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" s="50" t="s">
+      <c r="A37" s="43" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="51">
+      <c r="B37" s="44">
         <f>SUM(B22:B35)</f>
         <v>28836663.584121786</v>
       </c>
-      <c r="C37" s="51"/>
-      <c r="D37" s="51">
+      <c r="C37" s="44"/>
+      <c r="D37" s="44">
         <f>SUM(D22:D35)</f>
         <v>95160.989827601908</v>
       </c>
-      <c r="E37" s="51">
+      <c r="E37" s="44">
         <f>SUM(E22:E35)</f>
         <v>64859.010172398099</v>
       </c>
-      <c r="F37" s="51">
+      <c r="F37" s="44">
         <f>IFERROR(F35,"")</f>
         <v>0</v>
       </c>
@@ -3822,24 +4219,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="58" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="59" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
@@ -3863,16 +4260,16 @@
         <v>97</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D4" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E4" s="25"/>
-      <c r="F4" s="67" t="s">
+      <c r="F4" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="67"/>
+      <c r="G4" s="60"/>
       <c r="H4" s="25"/>
     </row>
     <row r="5" spans="1:8">
@@ -3930,7 +4327,7 @@
       </c>
       <c r="E7" s="25"/>
       <c r="F7" s="30" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G7" s="37" t="str">
         <f>IFERROR(C15/B15,"")</f>
@@ -4089,33 +4486,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="22.8">
-      <c r="B2" s="69" t="s">
+      <c r="B2" s="62" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
+      <c r="C2" s="62"/>
+      <c r="D2" s="62"/>
+      <c r="E2" s="62"/>
+      <c r="F2" s="62"/>
     </row>
     <row r="3" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="4" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B4" s="70" t="s">
+      <c r="B4" s="63" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="70"/>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
+      <c r="C4" s="63"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
     </row>
     <row r="5" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="6" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B6" s="71" t="s">
+      <c r="B6" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
     </row>
     <row r="7" spans="2:6" ht="21.75" customHeight="1">
       <c r="B7" s="16" t="s">
@@ -4147,34 +4544,34 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="16.8">
-      <c r="B9" s="72" t="s">
+      <c r="B9" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="E9" s="73">
+      <c r="C9" s="65"/>
+      <c r="E9" s="66">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(F8),C8&gt;0,F8&gt;0),SQRT(C8^2+F8^2),"Fyll inn a og b")</f>
         <v>5</v>
       </c>
-      <c r="F9" s="73"/>
+      <c r="F9" s="66"/>
     </row>
     <row r="10" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B10" s="68" t="s">
+      <c r="B10" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="12" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B12" s="71" t="s">
+      <c r="B12" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="71"/>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="71"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
     </row>
     <row r="13" spans="2:6" ht="9.75" customHeight="1">
       <c r="B13" s="16" t="s">
@@ -4206,34 +4603,34 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="16.8">
-      <c r="B15" s="72" t="s">
+      <c r="B15" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="72"/>
-      <c r="E15" s="73">
+      <c r="C15" s="65"/>
+      <c r="E15" s="66">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(F14),C14&gt;0,F14&gt;0,C14&gt;F14),SQRT(C14^2-F14^2),IF(C14&lt;=F14,"c må være større enn b","Fyll inn c og b"))</f>
         <v>3</v>
       </c>
-      <c r="F15" s="73"/>
+      <c r="F15" s="66"/>
     </row>
     <row r="16" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B16" s="68" t="s">
+      <c r="B16" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
     </row>
     <row r="17" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="18" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B18" s="71" t="s">
+      <c r="B18" s="64" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="64"/>
     </row>
     <row r="19" spans="2:6" ht="21.75" customHeight="1">
       <c r="B19" s="16" t="s">
@@ -4265,44 +4662,44 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="16.8">
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="E21" s="73">
+      <c r="C21" s="65"/>
+      <c r="E21" s="66">
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(F20),C20&gt;0,F20&gt;0,C20&gt;F20),SQRT(C20^2-F20^2),IF(C20&lt;=F20,"c må være større enn a","Fyll inn c og a"))</f>
         <v>4</v>
       </c>
-      <c r="F21" s="73"/>
+      <c r="F21" s="66"/>
     </row>
     <row r="22" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="61" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
     </row>
     <row r="23" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="24" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B24" s="74" t="s">
+      <c r="B24" s="67" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="74"/>
-      <c r="D24" s="74"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="67"/>
     </row>
     <row r="25" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B25" s="75" t="s">
+      <c r="B25" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="75"/>
-      <c r="E25" s="76" t="s">
+      <c r="C25" s="68"/>
+      <c r="E25" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="76"/>
+      <c r="F25" s="69"/>
     </row>
     <row r="26" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="27" spans="2:6" ht="21.75" customHeight="1"/>
@@ -4356,184 +4753,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="16.8">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="55" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="55"/>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="47" t="s">
         <v>115</v>
       </c>
-      <c r="B1" s="62"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="63"/>
-      <c r="B2" s="63"/>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="52" t="s">
+      <c r="B4" s="48">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B5" s="48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="54" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="54" t="s">
+      <c r="B6" s="54"/>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="47" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="55">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="55">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="61" t="s">
-        <v>120</v>
-      </c>
-      <c r="B6" s="61"/>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="54" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="56">
+      <c r="B7" s="49">
         <f>B4*(1+B5/100)</f>
         <v>1250</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="B8" s="56">
+      <c r="A8" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="B8" s="49">
         <f>B7-B4</f>
         <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="16.8" customHeight="1">
-      <c r="A11" s="62" t="s">
-        <v>123</v>
-      </c>
-      <c r="B11" s="62"/>
+      <c r="A11" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="B11" s="55"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="63"/>
-      <c r="B12" s="63"/>
+      <c r="A12" s="56"/>
+      <c r="B12" s="56"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="52" t="s">
+      <c r="A13" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="50" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="48">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="47" t="s">
         <v>116</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B15" s="48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="54" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="54" t="s">
-        <v>124</v>
-      </c>
-      <c r="B14" s="55">
-        <v>1250</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="54" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="55">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="61" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="61"/>
+      <c r="B16" s="54"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="54" t="s">
-        <v>125</v>
-      </c>
-      <c r="B17" s="56">
+      <c r="A17" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="49">
         <f>IF(1+B15/100=0,"Ugyldig: 0%",B14/(1+B15/100))</f>
         <v>1000</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="B18" s="56">
+      <c r="A18" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" s="49">
         <f>IF(ISNUMBER(B17),B14-B17,"")</f>
         <v>250</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="16.8" customHeight="1">
-      <c r="A21" s="62" t="s">
-        <v>126</v>
-      </c>
-      <c r="B21" s="62"/>
+      <c r="A21" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="B21" s="55"/>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="63"/>
-      <c r="B22" s="63"/>
+      <c r="A22" s="56"/>
+      <c r="B22" s="56"/>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="52" t="s">
-        <v>116</v>
-      </c>
-      <c r="B23" s="53" t="s">
+      <c r="A23" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="46" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="B24" s="48">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="47" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" s="48">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="54" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="54" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="55">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="54" t="s">
-        <v>127</v>
-      </c>
-      <c r="B25" s="55">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="61" t="s">
-        <v>120</v>
-      </c>
-      <c r="B26" s="61"/>
+      <c r="B26" s="54"/>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="B27" s="83">
+      <c r="A27" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="B27" s="76">
         <f>IF(B24=0,"Ugyldig: startverdi er 0",(B25-B24)/B24*100)/100</f>
         <v>1.5</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="54" t="s">
-        <v>122</v>
-      </c>
-      <c r="B28" s="84">
+      <c r="A28" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="B28" s="77">
         <f>B25-B24</f>
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="54" t="s">
-        <v>129</v>
-      </c>
-      <c r="B29" s="85" t="str">
+      <c r="A29" s="47" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="78" t="str">
         <f>IF(ISNUMBER(B27),TEXT(B27,"0.00")&amp;" %",B27)</f>
         <v>1.50 %</v>
       </c>
@@ -4560,20 +4957,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="78" t="s">
-        <v>132</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
+      <c r="A1" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" s="71"/>
+      <c r="C1" s="71"/>
+      <c r="D1" s="71"/>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A3" s="77" t="s">
+      <c r="A3" s="70" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="77"/>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
+      <c r="B3" s="70"/>
+      <c r="C3" s="70"/>
+      <c r="D3" s="70"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="21" t="s">
@@ -4654,12 +5051,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A11" s="77" t="s">
+      <c r="A11" s="70" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="77"/>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
+      <c r="B11" s="70"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="21" t="s">
@@ -4740,12 +5137,12 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A19" s="77" t="s">
+      <c r="A19" s="70" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="77"/>
-      <c r="C19" s="77"/>
-      <c r="D19" s="77"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="21" t="s">
@@ -4827,12 +5224,12 @@
     </row>
     <row r="27" spans="1:4" ht="19.5" customHeight="1"/>
     <row r="28" spans="1:4" ht="15.6">
-      <c r="A28" s="77" t="s">
+      <c r="A28" s="70" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="77"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="77"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="21" t="s">
@@ -4861,12 +5258,12 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.6">
-      <c r="A32" s="77" t="s">
+      <c r="A32" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="77"/>
-      <c r="C32" s="77"/>
-      <c r="D32" s="77"/>
+      <c r="B32" s="70"/>
+      <c r="C32" s="70"/>
+      <c r="D32" s="70"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="21" t="s">
@@ -4945,30 +5342,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
+      <c r="A1" s="72" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="80"/>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -4979,10 +5376,10 @@
         <f>AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;"")</f>
         <v>0</v>
       </c>
-      <c r="K3" s="81" t="s">
+      <c r="K3" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="81"/>
+      <c r="L3" s="74"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
       <c r="K4" s="4" t="s">
@@ -5082,11 +5479,11 @@
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),(IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),SUM(C8:C27),1)+1)/2,0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="82" t="str">
+      <c r="K8" s="75" t="str">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),"✅ Klar – se Histogram-fanen","⚠️ Fyll inn data i kolonne A og C")</f>
         <v>⚠️ Fyll inn data i kolonne A og C</v>
       </c>
-      <c r="L8" s="82"/>
+      <c r="L8" s="75"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
       <c r="A9" s="2"/>

--- a/SnorresMatteskjema.xlsx
+++ b/SnorresMatteskjema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\A\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3767B6D5-7F90-47EC-BC1D-A417D28D808E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33C7113B-A5E8-4549-B257-8BA9837FC441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="501" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1227,63 +1227,6 @@
     <xf numFmtId="0" fontId="33" fillId="27" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="1" fillId="33" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1293,49 +1236,61 @@
     <xf numFmtId="0" fontId="15" fillId="34" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="40" fillId="39" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="39" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="36" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="37" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="38" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="40" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="37" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="41" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="38" fillId="39" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="41" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="36" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1346,22 +1301,67 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="37" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="39" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="39" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="40" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="41" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="41" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="38" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="17" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -2975,352 +2975,340 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="23.4">
-      <c r="A1" s="79" t="s">
+      <c r="A1" s="81" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
-      <c r="F1" s="79"/>
-      <c r="G1" s="79"/>
-      <c r="H1" s="79"/>
-      <c r="I1" s="79"/>
-      <c r="J1" s="79"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="79"/>
-      <c r="M1" s="79"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
     </row>
     <row r="3" spans="1:13">
-      <c r="B3" s="80" t="s">
+      <c r="B3" s="82" t="s">
         <v>135</v>
       </c>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="82" t="s">
+      <c r="C3" s="73"/>
+      <c r="D3" s="73"/>
+      <c r="E3" s="73"/>
+      <c r="F3" s="83" t="s">
         <v>136</v>
       </c>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
       <c r="J3" s="84" t="s">
         <v>137</v>
       </c>
-      <c r="K3" s="85"/>
-      <c r="L3" s="85"/>
-      <c r="M3" s="85"/>
+      <c r="K3" s="77"/>
+      <c r="L3" s="77"/>
+      <c r="M3" s="77"/>
     </row>
     <row r="4" spans="1:13">
-      <c r="B4" s="81"/>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="85"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="85"/>
-      <c r="M4" s="85"/>
+      <c r="B4" s="73"/>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="75"/>
+      <c r="G4" s="75"/>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="77"/>
+      <c r="K4" s="77"/>
+      <c r="L4" s="77"/>
+      <c r="M4" s="77"/>
     </row>
     <row r="5" spans="1:13">
-      <c r="B5" s="81"/>
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="81"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="85"/>
-      <c r="K5" s="85"/>
-      <c r="L5" s="85"/>
-      <c r="M5" s="85"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="75"/>
+      <c r="G5" s="75"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
+      <c r="J5" s="77"/>
+      <c r="K5" s="77"/>
+      <c r="L5" s="77"/>
+      <c r="M5" s="77"/>
     </row>
     <row r="6" spans="1:13">
-      <c r="B6" s="81"/>
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="81"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="85"/>
-      <c r="L6" s="85"/>
-      <c r="M6" s="85"/>
+      <c r="B6" s="73"/>
+      <c r="C6" s="73"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="73"/>
+      <c r="F6" s="75"/>
+      <c r="G6" s="75"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
+      <c r="J6" s="77"/>
+      <c r="K6" s="77"/>
+      <c r="L6" s="77"/>
+      <c r="M6" s="77"/>
     </row>
     <row r="7" spans="1:13">
-      <c r="B7" s="98" t="s">
+      <c r="B7" s="85" t="s">
         <v>138</v>
       </c>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100" t="s">
+      <c r="C7" s="86"/>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="87" t="s">
         <v>102</v>
       </c>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="108" t="s">
+      <c r="G7" s="88"/>
+      <c r="H7" s="88"/>
+      <c r="I7" s="88"/>
+      <c r="J7" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="K7" s="109"/>
-      <c r="L7" s="109"/>
-      <c r="M7" s="109"/>
+      <c r="K7" s="90"/>
+      <c r="L7" s="90"/>
+      <c r="M7" s="90"/>
     </row>
     <row r="8" spans="1:13">
-      <c r="B8" s="99"/>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="99"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
-      <c r="J8" s="109"/>
-      <c r="K8" s="109"/>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
+      <c r="B8" s="86"/>
+      <c r="C8" s="86"/>
+      <c r="D8" s="86"/>
+      <c r="E8" s="86"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="88"/>
+      <c r="I8" s="88"/>
+      <c r="J8" s="90"/>
+      <c r="K8" s="90"/>
+      <c r="L8" s="90"/>
+      <c r="M8" s="90"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="B9" s="99"/>
-      <c r="C9" s="99"/>
-      <c r="D9" s="99"/>
-      <c r="E9" s="99"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="109"/>
-      <c r="K9" s="109"/>
-      <c r="L9" s="109"/>
-      <c r="M9" s="109"/>
+      <c r="B9" s="86"/>
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="88"/>
+      <c r="G9" s="88"/>
+      <c r="H9" s="88"/>
+      <c r="I9" s="88"/>
+      <c r="J9" s="90"/>
+      <c r="K9" s="90"/>
+      <c r="L9" s="90"/>
+      <c r="M9" s="90"/>
     </row>
     <row r="10" spans="1:13">
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="72" t="s">
         <v>107</v>
       </c>
-      <c r="C10" s="81"/>
-      <c r="D10" s="81"/>
-      <c r="E10" s="81"/>
-      <c r="F10" s="87" t="s">
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="74" t="s">
         <v>108</v>
       </c>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="88" t="s">
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
+      <c r="K10" s="77"/>
+      <c r="L10" s="77"/>
+      <c r="M10" s="77"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="B11" s="81"/>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="81"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="75"/>
+      <c r="G11" s="75"/>
+      <c r="H11" s="75"/>
+      <c r="I11" s="75"/>
+      <c r="J11" s="77"/>
+      <c r="K11" s="77"/>
+      <c r="L11" s="77"/>
+      <c r="M11" s="77"/>
     </row>
     <row r="12" spans="1:13">
-      <c r="B12" s="81"/>
-      <c r="C12" s="81"/>
-      <c r="D12" s="81"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="75"/>
+      <c r="G12" s="75"/>
+      <c r="H12" s="75"/>
+      <c r="I12" s="75"/>
+      <c r="J12" s="77"/>
+      <c r="K12" s="77"/>
+      <c r="L12" s="77"/>
+      <c r="M12" s="77"/>
     </row>
     <row r="16" spans="1:13">
-      <c r="B16" s="89" t="s">
+      <c r="B16" s="78" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="90"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="90"/>
-      <c r="F16" s="91" t="s">
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="79" t="s">
         <v>140</v>
       </c>
-      <c r="G16" s="92"/>
-      <c r="H16" s="92"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="93" t="s">
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="80" t="s">
         <v>141</v>
       </c>
-      <c r="K16" s="94"/>
-      <c r="L16" s="94"/>
-      <c r="M16" s="94"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
     </row>
     <row r="17" spans="2:13">
-      <c r="B17" s="90"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="90"/>
-      <c r="F17" s="92"/>
-      <c r="G17" s="92"/>
-      <c r="H17" s="92"/>
-      <c r="I17" s="92"/>
-      <c r="J17" s="94"/>
-      <c r="K17" s="94"/>
-      <c r="L17" s="94"/>
-      <c r="M17" s="94"/>
+      <c r="B17" s="67"/>
+      <c r="C17" s="67"/>
+      <c r="D17" s="67"/>
+      <c r="E17" s="67"/>
+      <c r="F17" s="69"/>
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
     </row>
     <row r="18" spans="2:13">
-      <c r="B18" s="90"/>
-      <c r="C18" s="90"/>
-      <c r="D18" s="90"/>
-      <c r="E18" s="90"/>
-      <c r="F18" s="92"/>
-      <c r="G18" s="92"/>
-      <c r="H18" s="92"/>
-      <c r="I18" s="92"/>
-      <c r="J18" s="94"/>
-      <c r="K18" s="94"/>
-      <c r="L18" s="94"/>
-      <c r="M18" s="94"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="69"/>
+      <c r="G18" s="69"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="71"/>
+      <c r="K18" s="71"/>
+      <c r="L18" s="71"/>
+      <c r="M18" s="71"/>
     </row>
     <row r="19" spans="2:13">
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="92"/>
-      <c r="G19" s="92"/>
-      <c r="H19" s="92"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="94"/>
-      <c r="K19" s="94"/>
-      <c r="L19" s="94"/>
-      <c r="M19" s="94"/>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="69"/>
+      <c r="G19" s="69"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="69"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
     </row>
     <row r="20" spans="2:13">
-      <c r="B20" s="102" t="s">
+      <c r="B20" s="60" t="s">
         <v>127</v>
       </c>
-      <c r="C20" s="103"/>
-      <c r="D20" s="103"/>
-      <c r="E20" s="103"/>
-      <c r="F20" s="104" t="s">
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="105"/>
-      <c r="H20" s="105"/>
-      <c r="I20" s="105"/>
-      <c r="J20" s="106" t="s">
+      <c r="G20" s="63"/>
+      <c r="H20" s="63"/>
+      <c r="I20" s="63"/>
+      <c r="J20" s="64" t="s">
         <v>105</v>
       </c>
-      <c r="K20" s="107"/>
-      <c r="L20" s="107"/>
-      <c r="M20" s="107"/>
+      <c r="K20" s="65"/>
+      <c r="L20" s="65"/>
+      <c r="M20" s="65"/>
     </row>
     <row r="21" spans="2:13">
-      <c r="B21" s="103"/>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="105"/>
-      <c r="G21" s="105"/>
-      <c r="H21" s="105"/>
-      <c r="I21" s="105"/>
-      <c r="J21" s="107"/>
-      <c r="K21" s="107"/>
-      <c r="L21" s="107"/>
-      <c r="M21" s="107"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="61"/>
+      <c r="F21" s="63"/>
+      <c r="G21" s="63"/>
+      <c r="H21" s="63"/>
+      <c r="I21" s="63"/>
+      <c r="J21" s="65"/>
+      <c r="K21" s="65"/>
+      <c r="L21" s="65"/>
+      <c r="M21" s="65"/>
     </row>
     <row r="22" spans="2:13">
-      <c r="B22" s="103"/>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="105"/>
-      <c r="G22" s="105"/>
-      <c r="H22" s="105"/>
-      <c r="I22" s="105"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="107"/>
-      <c r="M22" s="107"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="63"/>
+      <c r="G22" s="63"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="63"/>
+      <c r="J22" s="65"/>
+      <c r="K22" s="65"/>
+      <c r="L22" s="65"/>
+      <c r="M22" s="65"/>
     </row>
     <row r="23" spans="2:13">
-      <c r="B23" s="95" t="s">
+      <c r="B23" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="C23" s="90"/>
-      <c r="D23" s="90"/>
-      <c r="E23" s="90"/>
-      <c r="F23" s="96" t="s">
+      <c r="C23" s="67"/>
+      <c r="D23" s="67"/>
+      <c r="E23" s="67"/>
+      <c r="F23" s="68" t="s">
         <v>106</v>
       </c>
-      <c r="G23" s="92"/>
-      <c r="H23" s="92"/>
-      <c r="I23" s="92"/>
-      <c r="J23" s="97" t="s">
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="K23" s="94"/>
-      <c r="L23" s="94"/>
-      <c r="M23" s="94"/>
+      <c r="K23" s="71"/>
+      <c r="L23" s="71"/>
+      <c r="M23" s="71"/>
     </row>
     <row r="24" spans="2:13">
-      <c r="B24" s="90"/>
-      <c r="C24" s="90"/>
-      <c r="D24" s="90"/>
-      <c r="E24" s="90"/>
-      <c r="F24" s="92"/>
-      <c r="G24" s="92"/>
-      <c r="H24" s="92"/>
-      <c r="I24" s="92"/>
-      <c r="J24" s="94"/>
-      <c r="K24" s="94"/>
-      <c r="L24" s="94"/>
-      <c r="M24" s="94"/>
+      <c r="B24" s="67"/>
+      <c r="C24" s="67"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="67"/>
+      <c r="F24" s="69"/>
+      <c r="G24" s="69"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="69"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
     </row>
     <row r="25" spans="2:13">
-      <c r="B25" s="90"/>
-      <c r="C25" s="90"/>
-      <c r="D25" s="90"/>
-      <c r="E25" s="90"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="92"/>
-      <c r="I25" s="92"/>
-      <c r="J25" s="94"/>
-      <c r="K25" s="94"/>
-      <c r="L25" s="94"/>
-      <c r="M25" s="94"/>
+      <c r="B25" s="67"/>
+      <c r="C25" s="67"/>
+      <c r="D25" s="67"/>
+      <c r="E25" s="67"/>
+      <c r="F25" s="69"/>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="71"/>
+      <c r="K25" s="71"/>
+      <c r="L25" s="71"/>
+      <c r="M25" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="B20:E22"/>
-    <mergeCell ref="F20:I22"/>
-    <mergeCell ref="J20:M22"/>
-    <mergeCell ref="B23:E25"/>
-    <mergeCell ref="F23:I25"/>
-    <mergeCell ref="J23:M25"/>
-    <mergeCell ref="B10:E12"/>
-    <mergeCell ref="F10:I12"/>
-    <mergeCell ref="J10:M12"/>
-    <mergeCell ref="B16:E19"/>
-    <mergeCell ref="F16:I19"/>
-    <mergeCell ref="J16:M19"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="B3:E6"/>
     <mergeCell ref="F3:I6"/>
@@ -3328,6 +3316,18 @@
     <mergeCell ref="B7:E9"/>
     <mergeCell ref="F7:I9"/>
     <mergeCell ref="J7:M9"/>
+    <mergeCell ref="B10:E12"/>
+    <mergeCell ref="F10:I12"/>
+    <mergeCell ref="J10:M12"/>
+    <mergeCell ref="B16:E19"/>
+    <mergeCell ref="F16:I19"/>
+    <mergeCell ref="J16:M19"/>
+    <mergeCell ref="B20:E22"/>
+    <mergeCell ref="F20:I22"/>
+    <mergeCell ref="J20:M22"/>
+    <mergeCell ref="B23:E25"/>
+    <mergeCell ref="F23:I25"/>
+    <mergeCell ref="J23:M25"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B7" r:id="rId1" xr:uid="{9100B2D1-BB5C-473B-8117-69FF6BC0C34C}"/>
@@ -3366,13 +3366,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.2" customHeight="1">
-      <c r="A1" s="57" t="s">
+      <c r="A1" s="91" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="9" t="s">
@@ -4219,24 +4219,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="17.399999999999999">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
+      <c r="B1" s="92"/>
+      <c r="C1" s="92"/>
+      <c r="D1" s="92"/>
       <c r="E1" s="25"/>
       <c r="F1" s="25"/>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="59" t="s">
+      <c r="A2" s="93" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
+      <c r="B2" s="93"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
       <c r="E2" s="25"/>
       <c r="F2" s="25"/>
       <c r="G2" s="25"/>
@@ -4266,10 +4266,10 @@
         <v>110</v>
       </c>
       <c r="E4" s="25"/>
-      <c r="F4" s="60" t="s">
+      <c r="F4" s="94" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="60"/>
+      <c r="G4" s="94"/>
       <c r="H4" s="25"/>
     </row>
     <row r="5" spans="1:8">
@@ -4486,33 +4486,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" ht="22.8">
-      <c r="B2" s="62" t="s">
+      <c r="B2" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="C2" s="62"/>
-      <c r="D2" s="62"/>
-      <c r="E2" s="62"/>
-      <c r="F2" s="62"/>
+      <c r="C2" s="102"/>
+      <c r="D2" s="102"/>
+      <c r="E2" s="102"/>
+      <c r="F2" s="102"/>
     </row>
     <row r="3" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="4" spans="2:6" ht="27.75" customHeight="1">
-      <c r="B4" s="63" t="s">
+      <c r="B4" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
+      <c r="C4" s="103"/>
+      <c r="D4" s="103"/>
+      <c r="E4" s="103"/>
+      <c r="F4" s="103"/>
     </row>
     <row r="5" spans="2:6" ht="9.75" customHeight="1"/>
     <row r="6" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B6" s="64" t="s">
+      <c r="B6" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="99"/>
     </row>
     <row r="7" spans="2:6" ht="21.75" customHeight="1">
       <c r="B7" s="16" t="s">
@@ -4544,34 +4544,34 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="16.8">
-      <c r="B9" s="65" t="s">
+      <c r="B9" s="100" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="65"/>
-      <c r="E9" s="66">
+      <c r="C9" s="100"/>
+      <c r="E9" s="101">
         <f>IF(AND(ISNUMBER(C8),ISNUMBER(F8),C8&gt;0,F8&gt;0),SQRT(C8^2+F8^2),"Fyll inn a og b")</f>
         <v>5</v>
       </c>
-      <c r="F9" s="66"/>
+      <c r="F9" s="101"/>
     </row>
     <row r="10" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="95" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
-      <c r="E10" s="61"/>
-      <c r="F10" s="61"/>
+      <c r="C10" s="95"/>
+      <c r="D10" s="95"/>
+      <c r="E10" s="95"/>
+      <c r="F10" s="95"/>
     </row>
     <row r="11" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="12" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B12" s="64" t="s">
+      <c r="B12" s="99" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="64"/>
-      <c r="D12" s="64"/>
-      <c r="E12" s="64"/>
-      <c r="F12" s="64"/>
+      <c r="C12" s="99"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
     </row>
     <row r="13" spans="2:6" ht="9.75" customHeight="1">
       <c r="B13" s="16" t="s">
@@ -4603,34 +4603,34 @@
       </c>
     </row>
     <row r="15" spans="2:6" ht="16.8">
-      <c r="B15" s="65" t="s">
+      <c r="B15" s="100" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="65"/>
-      <c r="E15" s="66">
+      <c r="C15" s="100"/>
+      <c r="E15" s="101">
         <f>IF(AND(ISNUMBER(C14),ISNUMBER(F14),C14&gt;0,F14&gt;0,C14&gt;F14),SQRT(C14^2-F14^2),IF(C14&lt;=F14,"c må være større enn b","Fyll inn c og b"))</f>
         <v>3</v>
       </c>
-      <c r="F15" s="66"/>
+      <c r="F15" s="101"/>
     </row>
     <row r="16" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B16" s="61" t="s">
+      <c r="B16" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
+      <c r="C16" s="95"/>
+      <c r="D16" s="95"/>
+      <c r="E16" s="95"/>
+      <c r="F16" s="95"/>
     </row>
     <row r="17" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="18" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B18" s="64" t="s">
+      <c r="B18" s="99" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="64"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="99"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="99"/>
     </row>
     <row r="19" spans="2:6" ht="21.75" customHeight="1">
       <c r="B19" s="16" t="s">
@@ -4662,44 +4662,44 @@
       </c>
     </row>
     <row r="21" spans="2:6" ht="16.8">
-      <c r="B21" s="65" t="s">
+      <c r="B21" s="100" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="65"/>
-      <c r="E21" s="66">
+      <c r="C21" s="100"/>
+      <c r="E21" s="101">
         <f>IF(AND(ISNUMBER(C20),ISNUMBER(F20),C20&gt;0,F20&gt;0,C20&gt;F20),SQRT(C20^2-F20^2),IF(C20&lt;=F20,"c må være større enn a","Fyll inn c og a"))</f>
         <v>4</v>
       </c>
-      <c r="F21" s="66"/>
+      <c r="F21" s="101"/>
     </row>
     <row r="22" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B22" s="61" t="s">
+      <c r="B22" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="61"/>
-      <c r="D22" s="61"/>
-      <c r="E22" s="61"/>
-      <c r="F22" s="61"/>
+      <c r="C22" s="95"/>
+      <c r="D22" s="95"/>
+      <c r="E22" s="95"/>
+      <c r="F22" s="95"/>
     </row>
     <row r="23" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="24" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="67"/>
-      <c r="D24" s="67"/>
-      <c r="E24" s="67"/>
-      <c r="F24" s="67"/>
+      <c r="C24" s="96"/>
+      <c r="D24" s="96"/>
+      <c r="E24" s="96"/>
+      <c r="F24" s="96"/>
     </row>
     <row r="25" spans="2:6" ht="21.75" customHeight="1">
-      <c r="B25" s="68" t="s">
+      <c r="B25" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="C25" s="68"/>
-      <c r="E25" s="69" t="s">
+      <c r="C25" s="97"/>
+      <c r="E25" s="98" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="69"/>
+      <c r="F25" s="98"/>
     </row>
     <row r="26" spans="2:6" ht="21.75" customHeight="1"/>
     <row r="27" spans="2:6" ht="21.75" customHeight="1"/>
@@ -4717,6 +4717,12 @@
     <row r="39" ht="21.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="E9:F9"/>
     <mergeCell ref="B22:F22"/>
     <mergeCell ref="B24:F24"/>
     <mergeCell ref="B25:C25"/>
@@ -4728,12 +4734,6 @@
     <mergeCell ref="B18:F18"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="E9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4912,7 +4912,7 @@
       <c r="A27" s="47" t="s">
         <v>125</v>
       </c>
-      <c r="B27" s="76">
+      <c r="B27" s="57">
         <f>IF(B24=0,"Ugyldig: startverdi er 0",(B25-B24)/B24*100)/100</f>
         <v>1.5</v>
       </c>
@@ -4921,7 +4921,7 @@
       <c r="A28" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="77">
+      <c r="B28" s="58">
         <f>B25-B24</f>
         <v>30</v>
       </c>
@@ -4930,7 +4930,7 @@
       <c r="A29" s="47" t="s">
         <v>126</v>
       </c>
-      <c r="B29" s="78" t="str">
+      <c r="B29" s="59" t="str">
         <f>IF(ISNUMBER(B27),TEXT(B27,"0.00")&amp;" %",B27)</f>
         <v>1.50 %</v>
       </c>
@@ -4957,20 +4957,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24.75" customHeight="1">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="105" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
+      <c r="B1" s="105"/>
+      <c r="C1" s="105"/>
+      <c r="D1" s="105"/>
     </row>
     <row r="3" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A3" s="70" t="s">
+      <c r="A3" s="104" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="70"/>
-      <c r="C3" s="70"/>
-      <c r="D3" s="70"/>
+      <c r="B3" s="104"/>
+      <c r="C3" s="104"/>
+      <c r="D3" s="104"/>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="21" t="s">
@@ -5051,12 +5051,12 @@
       </c>
     </row>
     <row r="11" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A11" s="70" t="s">
+      <c r="A11" s="104" t="s">
         <v>61</v>
       </c>
-      <c r="B11" s="70"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
+      <c r="B11" s="104"/>
+      <c r="C11" s="104"/>
+      <c r="D11" s="104"/>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="21" t="s">
@@ -5137,12 +5137,12 @@
       </c>
     </row>
     <row r="19" spans="1:4" ht="19.5" customHeight="1">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="104" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="70"/>
-      <c r="C19" s="70"/>
-      <c r="D19" s="70"/>
+      <c r="B19" s="104"/>
+      <c r="C19" s="104"/>
+      <c r="D19" s="104"/>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="21" t="s">
@@ -5224,12 +5224,12 @@
     </row>
     <row r="27" spans="1:4" ht="19.5" customHeight="1"/>
     <row r="28" spans="1:4" ht="15.6">
-      <c r="A28" s="70" t="s">
+      <c r="A28" s="104" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="70"/>
-      <c r="C28" s="70"/>
-      <c r="D28" s="70"/>
+      <c r="B28" s="104"/>
+      <c r="C28" s="104"/>
+      <c r="D28" s="104"/>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="21" t="s">
@@ -5258,12 +5258,12 @@
       </c>
     </row>
     <row r="32" spans="1:4" ht="15.6">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="104" t="s">
         <v>87</v>
       </c>
-      <c r="B32" s="70"/>
-      <c r="C32" s="70"/>
-      <c r="D32" s="70"/>
+      <c r="B32" s="104"/>
+      <c r="C32" s="104"/>
+      <c r="D32" s="104"/>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="21" t="s">
@@ -5342,30 +5342,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="30" customHeight="1">
-      <c r="A1" s="72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="A1" s="106" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="106"/>
+      <c r="C1" s="106"/>
+      <c r="D1" s="106"/>
+      <c r="E1" s="106"/>
+      <c r="F1" s="106"/>
+      <c r="G1" s="106"/>
+      <c r="H1" s="106"/>
+      <c r="I1" s="106"/>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="73"/>
-      <c r="C2" s="73"/>
-      <c r="D2" s="73"/>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73"/>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
+      <c r="B2" s="107"/>
+      <c r="C2" s="107"/>
+      <c r="D2" s="107"/>
+      <c r="E2" s="107"/>
+      <c r="F2" s="107"/>
+      <c r="G2" s="107"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="107"/>
     </row>
     <row r="3" spans="1:12" ht="21.75" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -5376,10 +5376,10 @@
         <f>AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;"")</f>
         <v>0</v>
       </c>
-      <c r="K3" s="74" t="s">
+      <c r="K3" s="108" t="s">
         <v>3</v>
       </c>
-      <c r="L3" s="74"/>
+      <c r="L3" s="108"/>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1">
       <c r="K4" s="4" t="s">
@@ -5479,11 +5479,11 @@
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),(IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),SUM(C8:C27),1)+1)/2,0)</f>
         <v>0</v>
       </c>
-      <c r="K8" s="75" t="str">
+      <c r="K8" s="109" t="str">
         <f>IF(AND(COUNT(A8:A27)&gt;0,COUNT(A8:A27)=COUNT(C8:C27),B3&lt;&gt;""),"✅ Klar – se Histogram-fanen","⚠️ Fyll inn data i kolonne A og C")</f>
         <v>⚠️ Fyll inn data i kolonne A og C</v>
       </c>
-      <c r="L8" s="75"/>
+      <c r="L8" s="109"/>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1">
       <c r="A9" s="2"/>
